--- a/ESP32_S3_SQD_Project_WBS.xlsx
+++ b/ESP32_S3_SQD_Project_WBS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f91d42a59b2d5e5/SQD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\SQD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{C84441A9-493A-415C-B430-AB0EFCA297E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7038D520-20FD-4BCA-A22B-CE50EC350255}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14085" yWindow="-16200" windowWidth="29010" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14730" yWindow="-16320" windowWidth="57840" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -3831,7 +3831,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.37037037037037041</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4318,14 +4318,14 @@
       </c>
       <c r="E5" s="12">
         <f>Control!B11</f>
-        <v>0.11553133514986372</v>
+        <v>0.17111716621253398</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H5" s="12">
         <f>Control!B12</f>
-        <v>0.10463215258855582</v>
+        <v>0.16021798365122608</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1"/>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E7" s="11">
         <f>Control!B14</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>9</v>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="F13" s="6">
         <f>IFERROR(SUMIF(WBS!$B$5:$B$137,A13,WBS!$T$5:$T$137)/SUMIF(WBS!$B$5:$B$137,A13,WBS!$R$5:$R$137),0)</f>
-        <v>0.37037037037037041</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6">
         <f t="shared" si="0"/>
-        <v>0.37037037037037041</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4">
         <f>COUNTIF(WBS!$B$5:$B$137,A13)</f>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="I13" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A13,WBS!$U$5:$U$137,"Complete")</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A13,WBS!$U$5:$U$137,"Late")</f>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="B11" s="6">
         <f>SUM(WBS!T5:T137)</f>
-        <v>0.11553133514986372</v>
+        <v>0.17111716621253398</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>69</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B12" s="6">
         <f>B11-B10</f>
-        <v>0.10463215258855582</v>
+        <v>0.16021798365122608</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>70</v>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B14" s="4">
         <f>COUNTIF(WBS!U5:U137,"Complete")</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>72</v>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="14">
         <f t="shared" si="0"/>
@@ -6398,11 +6398,11 @@
       </c>
       <c r="T20" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.4495912806539499E-3</v>
       </c>
       <c r="U20" t="str">
         <f>IF(Q20&gt;=1,"Complete",IF(Q20&gt;0,"In Progress",IF(Control!$B$7&lt;H20,"Not Started",IF(Control!$B$7&gt;I20,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V20" s="15">
         <v>46272</v>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="14">
         <f t="shared" si="0"/>
@@ -6471,11 +6471,11 @@
       </c>
       <c r="T21" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.08991825613079E-2</v>
       </c>
       <c r="U21" t="str">
         <f>IF(Q21&gt;=1,"Complete",IF(Q21&gt;0,"In Progress",IF(Control!$B$7&lt;H21,"Not Started",IF(Control!$B$7&gt;I21,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V21" s="15">
         <v>46272</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="14">
         <f t="shared" si="0"/>
@@ -6544,11 +6544,11 @@
       </c>
       <c r="T22" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.08991825613079E-2</v>
       </c>
       <c r="U22" t="str">
         <f>IF(Q22&gt;=1,"Complete",IF(Q22&gt;0,"In Progress",IF(Control!$B$7&lt;H22,"Not Started",IF(Control!$B$7&gt;I22,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V22" s="15">
         <v>46279</v>
@@ -6605,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="14">
         <f t="shared" si="0"/>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="T23" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.4495912806539499E-3</v>
       </c>
       <c r="U23" t="str">
         <f>IF(Q23&gt;=1,"Complete",IF(Q23&gt;0,"In Progress",IF(Control!$B$7&lt;H23,"Not Started",IF(Control!$B$7&gt;I23,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V23" s="15">
         <v>46286</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="14">
         <f t="shared" si="0"/>
@@ -6690,11 +6690,11 @@
       </c>
       <c r="T24" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.08991825613079E-2</v>
       </c>
       <c r="U24" t="str">
         <f>IF(Q24&gt;=1,"Complete",IF(Q24&gt;0,"In Progress",IF(Control!$B$7&lt;H24,"Not Started",IF(Control!$B$7&gt;I24,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V24" s="15">
         <v>46286</v>
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="14">
         <f t="shared" si="0"/>
@@ -6763,11 +6763,11 @@
       </c>
       <c r="T25" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.4495912806539499E-3</v>
       </c>
       <c r="U25" t="str">
         <f>IF(Q25&gt;=1,"Complete",IF(Q25&gt;0,"In Progress",IF(Control!$B$7&lt;H25,"Not Started",IF(Control!$B$7&gt;I25,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V25" s="15">
         <v>46293</v>
@@ -6827,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="Q26" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="14">
         <f t="shared" si="0"/>
@@ -6839,11 +6839,11 @@
       </c>
       <c r="T26" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5395095367847397E-3</v>
       </c>
       <c r="U26" t="str">
         <f>IF(Q26&gt;=1,"Complete",IF(Q26&gt;0,"In Progress",IF(Control!$B$7&lt;H26,"Not Started",IF(Control!$B$7&gt;I26,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V26" s="15">
         <v>46293</v>
@@ -15314,22 +15314,22 @@
       </c>
       <c r="H8" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A8,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A8,WBS!$R$5:$R$137),0)</f>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4">
         <v>3</v>
       </c>
       <c r="K8" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A8,WBS!$U$5:$U$137,"Complete")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="4" t="str">
         <f>IF(H8&gt;=1,"Complete",IF(H8&gt;0,"In Progress",IF(Control!$B$7&lt;D8,"Not Started",IF(Control!$B$7&gt;E8,"Late","Ready"))))</f>
-        <v>In Progress</v>
+        <v>Complete</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -15357,22 +15357,22 @@
       </c>
       <c r="H9" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A9,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A9,WBS!$R$5:$R$137),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4">
         <v>3</v>
       </c>
       <c r="K9" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A9,WBS!$U$5:$U$137,"Complete")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="4" t="str">
         <f>IF(H9&gt;=1,"Complete",IF(H9&gt;0,"In Progress",IF(Control!$B$7&lt;D9,"Not Started",IF(Control!$B$7&gt;E9,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -15400,22 +15400,22 @@
       </c>
       <c r="H10" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A10,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A10,WBS!$R$5:$R$137),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4">
         <v>3</v>
       </c>
       <c r="K10" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A10,WBS!$U$5:$U$137,"Complete")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="4" t="str">
         <f>IF(H10&gt;=1,"Complete",IF(H10&gt;0,"In Progress",IF(Control!$B$7&lt;D10,"Not Started",IF(Control!$B$7&gt;E10,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="I4" s="6">
         <f>IF(A4=Control!$B$7,Control!$B$11,"")</f>
-        <v>0.11553133514986372</v>
+        <v>0.17111716621253398</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="42.75">

--- a/ESP32_S3_SQD_Project_WBS.xlsx
+++ b/ESP32_S3_SQD_Project_WBS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\SQD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f91d42a59b2d5e5/SQD_WBS_Backups/B4.3_WBS_Recovery_20260726_091129/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC2B6BFE-A532-4185-87E4-86725BF234C3}"/>
   <bookViews>
     <workbookView xWindow="-14730" yWindow="-16320" windowWidth="57840" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1049">
   <si>
     <t>ESP32-S3 Solo Program Dashboard</t>
   </si>
@@ -3319,6 +3319,9 @@
   </si>
   <si>
     <t>Parthasarathy CP</t>
+  </si>
+  <si>
+    <t>Architecture: docs/phase-c/C1.1_System_Architecture.md | PR: https://github.com/CPParthasarathy/SQD/pull/19 | Main: a56bb119c16f1f61adc0c9ab7c848496d6a2b52a | CI: https://github.com/CPParthasarathy/SQD/actions/runs/30207286673 (Quality contracts and all three ESP-IDF profiles green)</t>
   </si>
 </sst>
 </file>
@@ -3834,7 +3837,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.9920318725099608E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4318,14 +4321,14 @@
       </c>
       <c r="E5" s="12">
         <f>Control!B11</f>
-        <v>0.17111716621253398</v>
+        <v>0.17656675749318793</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H5" s="12">
         <f>Control!B12</f>
-        <v>0.16021798365122608</v>
+        <v>0.16566757493188003</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1"/>
@@ -4342,7 +4345,7 @@
       </c>
       <c r="E7" s="11">
         <f>Control!B14</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>9</v>
@@ -4488,11 +4491,11 @@
       </c>
       <c r="F14" s="6">
         <f>IFERROR(SUMIF(WBS!$B$5:$B$137,A14,WBS!$T$5:$T$137)/SUMIF(WBS!$B$5:$B$137,A14,WBS!$R$5:$R$137),0)</f>
-        <v>0</v>
+        <v>1.9920318725099608E-2</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.9920318725099608E-2</v>
       </c>
       <c r="H14" s="4">
         <f>COUNTIF(WBS!$B$5:$B$137,A14)</f>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="I14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Complete")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Late")</f>
@@ -4947,7 +4950,7 @@
       </c>
       <c r="B11" s="6">
         <f>SUM(WBS!T5:T137)</f>
-        <v>0.17111716621253398</v>
+        <v>0.17656675749318793</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>69</v>
@@ -4962,7 +4965,7 @@
       </c>
       <c r="B12" s="6">
         <f>B11-B10</f>
-        <v>0.16021798365122608</v>
+        <v>0.16566757493188003</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>70</v>
@@ -4992,7 +4995,7 @@
       </c>
       <c r="B14" s="4">
         <f>COUNTIF(WBS!U5:U137,"Complete")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>72</v>
@@ -6119,7 +6122,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" t="s">
         <v>165</v>
       </c>
@@ -6192,7 +6195,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -6265,7 +6268,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>175</v>
       </c>
@@ -6338,7 +6341,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>179</v>
       </c>
@@ -6411,7 +6414,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>183</v>
       </c>
@@ -6484,7 +6487,7 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>189</v>
       </c>
@@ -6557,7 +6560,7 @@
         <v>46292</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>193</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>46292</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -6703,7 +6706,7 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>203</v>
       </c>
@@ -6776,7 +6779,7 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>207</v>
       </c>
@@ -6852,7 +6855,7 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>212</v>
       </c>
@@ -6900,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="14">
         <f t="shared" si="0"/>
@@ -6912,11 +6915,11 @@
       </c>
       <c r="T27" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.4495912806539499E-3</v>
       </c>
       <c r="U27" t="str">
         <f>IF(Q27&gt;=1,"Complete",IF(Q27&gt;0,"In Progress",IF(Control!$B$7&lt;H27,"Not Started",IF(Control!$B$7&gt;I27,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V27" s="15">
         <v>46300</v>
@@ -6924,8 +6927,11 @@
       <c r="W27" s="15">
         <v>46306</v>
       </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="X27" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
       <c r="A28" t="s">
         <v>218</v>
       </c>
@@ -6998,7 +7004,7 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>222</v>
       </c>
@@ -7071,7 +7077,7 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>226</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>232</v>
       </c>
@@ -7217,7 +7223,7 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>236</v>
       </c>
@@ -15443,22 +15449,22 @@
       </c>
       <c r="H11" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A11,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A11,WBS!$R$5:$R$137),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J11" s="4">
         <v>3</v>
       </c>
       <c r="K11" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A11,WBS!$U$5:$U$137,"Complete")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4" t="str">
         <f>IF(H11&gt;=1,"Complete",IF(H11&gt;0,"In Progress",IF(Control!$B$7&lt;D11,"Not Started",IF(Control!$B$7&gt;E11,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -16969,7 +16975,7 @@
       </c>
       <c r="I4" s="6">
         <f>IF(A4=Control!$B$7,Control!$B$11,"")</f>
-        <v>0.17111716621253398</v>
+        <v>0.17656675749318793</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="42.75">

--- a/ESP32_S3_SQD_Project_WBS.xlsx
+++ b/ESP32_S3_SQD_Project_WBS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f91d42a59b2d5e5/SQD_WBS_Backups/B4.3_WBS_Recovery_20260726_091129/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f91d42a59b2d5e5/SQD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC2B6BFE-A532-4185-87E4-86725BF234C3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3774EB4-4559-4205-8B47-D0DF71676CF7}"/>
   <bookViews>
     <workbookView xWindow="-14730" yWindow="-16320" windowWidth="57840" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1050">
   <si>
     <t>ESP32-S3 Solo Program Dashboard</t>
   </si>
@@ -3322,6 +3322,9 @@
   </si>
   <si>
     <t>Architecture: docs/phase-c/C1.1_System_Architecture.md | PR: https://github.com/CPParthasarathy/SQD/pull/19 | Main: a56bb119c16f1f61adc0c9ab7c848496d6a2b52a | CI: https://github.com/CPParthasarathy/SQD/actions/runs/30207286673 (Quality contracts and all three ESP-IDF profiles green)</t>
+  </si>
+  <si>
+    <t>Specification: docs/phase-c/C1.2_Component_Interface_and_Runtime_Contracts.md | Contract: tools/ci/c1_2_component_contract.json | PR: https://github.com/CPParthasarathy/SQD/pull/21 | Main: bad1c88dd56e584d819c612055876a298c1e9c64 | CI: https://github.com/CPParthasarathy/SQD/actions/runs/30696078035 (Quality contracts and all three ESP-IDF profiles green; post-merge verifier and 32 host tests passed)</t>
   </si>
 </sst>
 </file>
@@ -3837,7 +3840,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9920318725099608E-2</c:v>
+                  <c:v>5.9760956175298828E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4321,14 +4324,14 @@
       </c>
       <c r="E5" s="12">
         <f>Control!B11</f>
-        <v>0.17656675749318793</v>
+        <v>0.18746594005449582</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H5" s="12">
         <f>Control!B12</f>
-        <v>0.16566757493188003</v>
+        <v>0.17656675749318793</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1"/>
@@ -4345,7 +4348,7 @@
       </c>
       <c r="E7" s="11">
         <f>Control!B14</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>9</v>
@@ -4491,11 +4494,11 @@
       </c>
       <c r="F14" s="6">
         <f>IFERROR(SUMIF(WBS!$B$5:$B$137,A14,WBS!$T$5:$T$137)/SUMIF(WBS!$B$5:$B$137,A14,WBS!$R$5:$R$137),0)</f>
-        <v>1.9920318725099608E-2</v>
+        <v>5.9760956175298828E-2</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" si="0"/>
-        <v>1.9920318725099608E-2</v>
+        <v>5.9760956175298828E-2</v>
       </c>
       <c r="H14" s="4">
         <f>COUNTIF(WBS!$B$5:$B$137,A14)</f>
@@ -4503,7 +4506,7 @@
       </c>
       <c r="I14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Complete")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Late")</f>
@@ -4950,7 +4953,7 @@
       </c>
       <c r="B11" s="6">
         <f>SUM(WBS!T5:T137)</f>
-        <v>0.17656675749318793</v>
+        <v>0.18746594005449582</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>69</v>
@@ -4965,7 +4968,7 @@
       </c>
       <c r="B12" s="6">
         <f>B11-B10</f>
-        <v>0.16566757493188003</v>
+        <v>0.17656675749318793</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>70</v>
@@ -4995,7 +4998,7 @@
       </c>
       <c r="B14" s="4">
         <f>COUNTIF(WBS!U5:U137,"Complete")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>72</v>
@@ -6979,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="14">
         <f t="shared" si="0"/>
@@ -6991,17 +6994,20 @@
       </c>
       <c r="T28" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.08991825613079E-2</v>
       </c>
       <c r="U28" t="str">
         <f>IF(Q28&gt;=1,"Complete",IF(Q28&gt;0,"In Progress",IF(Control!$B$7&lt;H28,"Not Started",IF(Control!$B$7&gt;I28,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V28" s="15">
         <v>46300</v>
       </c>
       <c r="W28" s="15">
         <v>46313</v>
+      </c>
+      <c r="X28" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -15449,18 +15455,18 @@
       </c>
       <c r="H11" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A11,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A11,WBS!$R$5:$R$137),0)</f>
-        <v>0.25</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="J11" s="4">
         <v>3</v>
       </c>
       <c r="K11" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A11,WBS!$U$5:$U$137,"Complete")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4" t="str">
         <f>IF(H11&gt;=1,"Complete",IF(H11&gt;0,"In Progress",IF(Control!$B$7&lt;D11,"Not Started",IF(Control!$B$7&gt;E11,"Late","Ready"))))</f>
@@ -16975,7 +16981,7 @@
       </c>
       <c r="I4" s="6">
         <f>IF(A4=Control!$B$7,Control!$B$11,"")</f>
-        <v>0.17656675749318793</v>
+        <v>0.18746594005449582</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="42.75">

--- a/ESP32_S3_SQD_Project_WBS.xlsx
+++ b/ESP32_S3_SQD_Project_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f91d42a59b2d5e5/SQD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3774EB4-4559-4205-8B47-D0DF71676CF7}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7B4A80D-B986-4F5E-91F4-2A851EA0D048}"/>
   <bookViews>
     <workbookView xWindow="-14730" yWindow="-16320" windowWidth="57840" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1051">
   <si>
     <t>ESP32-S3 Solo Program Dashboard</t>
   </si>
@@ -724,18 +724,12 @@
     <t>C2</t>
   </si>
   <si>
-    <t>Board support package</t>
-  </si>
-  <si>
     <t>Define board pins, active levels, pulls, electrical capabilities and revision detection</t>
   </si>
   <si>
     <t>Board pin map and revision strategy</t>
   </si>
   <si>
-    <t>All board-specific data is isolated in the BSP</t>
-  </si>
-  <si>
     <t>C2.2</t>
   </si>
   <si>
@@ -2228,12 +2222,6 @@
   </si>
   <si>
     <t>Hardware revision support</t>
-  </si>
-  <si>
-    <t>Define hardware compatibility matrix and update board revision detection/BSP</t>
-  </si>
-  <si>
-    <t>Hardware compatibility matrix and BSP update</t>
   </si>
   <si>
     <t>Firmware compatibility range is explicit</t>
@@ -3172,13 +3160,6 @@
     <t>G2.3, G5.1</t>
   </si>
   <si>
-    <t>G2.3: Operate incident review and corrective-action loop during stabilization
-G5.1: Define hardware compatibility matrix and update board revision detection/BSP</t>
-  </si>
-  <si>
-    <t>G5.1: Hardware compatibility matrix and BSP update</t>
-  </si>
-  <si>
     <t>G2.3, G5.2</t>
   </si>
   <si>
@@ -3325,6 +3306,28 @@
   </si>
   <si>
     <t>Specification: docs/phase-c/C1.2_Component_Interface_and_Runtime_Contracts.md | Contract: tools/ci/c1_2_component_contract.json | PR: https://github.com/CPParthasarathy/SQD/pull/21 | Main: bad1c88dd56e584d819c612055876a298c1e9c64 | CI: https://github.com/CPParthasarathy/SQD/actions/runs/30696078035 (Quality contracts and all three ESP-IDF profiles green; post-merge verifier and 32 host tests passed)</t>
+  </si>
+  <si>
+    <t>Board and hardware foundation</t>
+  </si>
+  <si>
+    <t>All board-specific data is isolated in components/board</t>
+  </si>
+  <si>
+    <t>Define hardware compatibility matrix and update board revision detection in components/board</t>
+  </si>
+  <si>
+    <t>Hardware compatibility matrix and components/board update</t>
+  </si>
+  <si>
+    <t>G2.3: Operate incident review and corrective-action loop during stabilization
+G5.1: Define hardware compatibility matrix and update board revision detection in components/board</t>
+  </si>
+  <si>
+    <t>G5.1: Hardware compatibility matrix and components/board update</t>
+  </si>
+  <si>
+    <t>Gate G-C accepted 2026-08-02 | Record: docs/phase-c/C1.3_Architecture_Review_and_Gate.md | PR: https://github.com/CPParthasarathy/SQD/pull/23 | Accepted main: bd995912fb5632394f6aa29b146f17ec9dcdcf6d | CI: https://github.com/CPParthasarathy/SQD/actions/runs/30745138225 (4/4 PASS) | Architecture: 11/11 PASS | C1.3 tests: 6/6 PASS | Host tests: 38/38 PASS</t>
   </si>
 </sst>
 </file>
@@ -3840,7 +3843,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.9760956175298828E-2</c:v>
+                  <c:v>7.9681274900398433E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4022,6 +4025,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4324,14 +4331,14 @@
       </c>
       <c r="E5" s="12">
         <f>Control!B11</f>
-        <v>0.18746594005449582</v>
+        <v>0.19291553133514977</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H5" s="12">
         <f>Control!B12</f>
-        <v>0.17656675749318793</v>
+        <v>0.18201634877384187</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1"/>
@@ -4348,7 +4355,7 @@
       </c>
       <c r="E7" s="11">
         <f>Control!B14</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>9</v>
@@ -4494,11 +4501,11 @@
       </c>
       <c r="F14" s="6">
         <f>IFERROR(SUMIF(WBS!$B$5:$B$137,A14,WBS!$T$5:$T$137)/SUMIF(WBS!$B$5:$B$137,A14,WBS!$R$5:$R$137),0)</f>
-        <v>5.9760956175298828E-2</v>
+        <v>7.9681274900398433E-2</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" si="0"/>
-        <v>5.9760956175298828E-2</v>
+        <v>7.9681274900398433E-2</v>
       </c>
       <c r="H14" s="4">
         <f>COUNTIF(WBS!$B$5:$B$137,A14)</f>
@@ -4506,7 +4513,7 @@
       </c>
       <c r="I14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Complete")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Late")</f>
@@ -4867,7 +4874,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>58</v>
@@ -4953,7 +4960,7 @@
       </c>
       <c r="B11" s="6">
         <f>SUM(WBS!T5:T137)</f>
-        <v>0.18746594005449582</v>
+        <v>0.19291553133514977</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>69</v>
@@ -4968,7 +4975,7 @@
       </c>
       <c r="B12" s="6">
         <f>B11-B10</f>
-        <v>0.17656675749318793</v>
+        <v>0.18201634877384187</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>70</v>
@@ -4998,7 +5005,7 @@
       </c>
       <c r="B14" s="4">
         <f>COUNTIF(WBS!U5:U137,"Complete")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>72</v>
@@ -6931,7 +6938,7 @@
         <v>46306</v>
       </c>
       <c r="X27" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -7007,7 +7014,7 @@
         <v>46313</v>
       </c>
       <c r="X28" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -7058,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="14">
         <f t="shared" si="0"/>
@@ -7070,17 +7077,20 @@
       </c>
       <c r="T29" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.4495912806539499E-3</v>
       </c>
       <c r="U29" t="str">
         <f>IF(Q29&gt;=1,"Complete",IF(Q29&gt;0,"In Progress",IF(Control!$B$7&lt;H29,"Not Started",IF(Control!$B$7&gt;I29,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V29" s="15">
         <v>46307</v>
       </c>
       <c r="W29" s="15">
         <v>46313</v>
+      </c>
+      <c r="X29" t="s">
+        <v>1050</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -7097,10 +7107,10 @@
         <v>227</v>
       </c>
       <c r="E30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F30" t="s">
         <v>228</v>
-      </c>
-      <c r="F30" t="s">
-        <v>229</v>
       </c>
       <c r="G30" t="s">
         <v>222</v>
@@ -7121,10 +7131,10 @@
         <v>57</v>
       </c>
       <c r="M30" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N30" t="s">
-        <v>231</v>
+        <v>1045</v>
       </c>
       <c r="P30" s="14">
         <f>IF(Control!$B$7&lt;H30,0,IF(Control!$B$7&gt;=I30,1,(Control!$B$7-H30+1)/J30))</f>
@@ -7158,7 +7168,7 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
@@ -7170,10 +7180,10 @@
         <v>227</v>
       </c>
       <c r="E31" t="s">
-        <v>228</v>
+        <v>1044</v>
       </c>
       <c r="F31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G31" t="s">
         <v>226</v>
@@ -7194,10 +7204,10 @@
         <v>57</v>
       </c>
       <c r="M31" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P31" s="14">
         <f>IF(Control!$B$7&lt;H31,0,IF(Control!$B$7&gt;=I31,1,(Control!$B$7-H31+1)/J31))</f>
@@ -7231,7 +7241,7 @@
     </row>
     <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
@@ -7243,13 +7253,13 @@
         <v>227</v>
       </c>
       <c r="E32" t="s">
-        <v>228</v>
+        <v>1044</v>
       </c>
       <c r="F32" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H32">
         <v>16</v>
@@ -7267,10 +7277,10 @@
         <v>57</v>
       </c>
       <c r="M32" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N32" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P32" s="14">
         <f>IF(Control!$B$7&lt;H32,0,IF(Control!$B$7&gt;=I32,1,(Control!$B$7-H32+1)/J32))</f>
@@ -7304,7 +7314,7 @@
     </row>
     <row r="33" spans="1:23">
       <c r="A33" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s">
         <v>27</v>
@@ -7313,16 +7323,16 @@
         <v>28</v>
       </c>
       <c r="D33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" t="s">
+        <v>240</v>
+      </c>
+      <c r="F33" t="s">
         <v>241</v>
       </c>
-      <c r="E33" t="s">
-        <v>242</v>
-      </c>
-      <c r="F33" t="s">
-        <v>243</v>
-      </c>
       <c r="G33" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H33">
         <v>18</v>
@@ -7340,10 +7350,10 @@
         <v>57</v>
       </c>
       <c r="M33" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N33" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P33" s="14">
         <f>IF(Control!$B$7&lt;H33,0,IF(Control!$B$7&gt;=I33,1,(Control!$B$7-H33+1)/J33))</f>
@@ -7377,7 +7387,7 @@
     </row>
     <row r="34" spans="1:23">
       <c r="A34" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B34" t="s">
         <v>27</v>
@@ -7386,16 +7396,16 @@
         <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E34" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F34" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G34" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H34">
         <v>19</v>
@@ -7413,10 +7423,10 @@
         <v>57</v>
       </c>
       <c r="M34" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P34" s="14">
         <f>IF(Control!$B$7&lt;H34,0,IF(Control!$B$7&gt;=I34,1,(Control!$B$7-H34+1)/J34))</f>
@@ -7450,7 +7460,7 @@
     </row>
     <row r="35" spans="1:23">
       <c r="A35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
@@ -7459,16 +7469,16 @@
         <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E35" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G35" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H35">
         <v>20</v>
@@ -7486,10 +7496,10 @@
         <v>57</v>
       </c>
       <c r="M35" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N35" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P35" s="14">
         <f>IF(Control!$B$7&lt;H35,0,IF(Control!$B$7&gt;=I35,1,(Control!$B$7-H35+1)/J35))</f>
@@ -7523,7 +7533,7 @@
     </row>
     <row r="36" spans="1:23">
       <c r="A36" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B36" t="s">
         <v>27</v>
@@ -7532,16 +7542,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F36" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G36" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H36">
         <v>21</v>
@@ -7559,10 +7569,10 @@
         <v>57</v>
       </c>
       <c r="M36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N36" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P36" s="14">
         <f>IF(Control!$B$7&lt;H36,0,IF(Control!$B$7&gt;=I36,1,(Control!$B$7-H36+1)/J36))</f>
@@ -7596,7 +7606,7 @@
     </row>
     <row r="37" spans="1:23">
       <c r="A37" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B37" t="s">
         <v>27</v>
@@ -7605,13 +7615,13 @@
         <v>28</v>
       </c>
       <c r="D37" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" t="s">
+        <v>260</v>
+      </c>
+      <c r="F37" t="s">
         <v>261</v>
-      </c>
-      <c r="E37" t="s">
-        <v>262</v>
-      </c>
-      <c r="F37" t="s">
-        <v>263</v>
       </c>
       <c r="G37" t="s">
         <v>222</v>
@@ -7632,10 +7642,10 @@
         <v>57</v>
       </c>
       <c r="M37" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P37" s="14">
         <f>IF(Control!$B$7&lt;H37,0,IF(Control!$B$7&gt;=I37,1,(Control!$B$7-H37+1)/J37))</f>
@@ -7669,7 +7679,7 @@
     </row>
     <row r="38" spans="1:23">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B38" t="s">
         <v>27</v>
@@ -7678,16 +7688,16 @@
         <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G38" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H38">
         <v>17</v>
@@ -7705,10 +7715,10 @@
         <v>57</v>
       </c>
       <c r="M38" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P38" s="14">
         <f>IF(Control!$B$7&lt;H38,0,IF(Control!$B$7&gt;=I38,1,(Control!$B$7-H38+1)/J38))</f>
@@ -7742,7 +7752,7 @@
     </row>
     <row r="39" spans="1:23">
       <c r="A39" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s">
         <v>27</v>
@@ -7751,16 +7761,16 @@
         <v>28</v>
       </c>
       <c r="D39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G39" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H39">
         <v>18</v>
@@ -7778,10 +7788,10 @@
         <v>57</v>
       </c>
       <c r="M39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N39" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P39" s="14">
         <f>IF(Control!$B$7&lt;H39,0,IF(Control!$B$7&gt;=I39,1,(Control!$B$7-H39+1)/J39))</f>
@@ -7815,7 +7825,7 @@
     </row>
     <row r="40" spans="1:23">
       <c r="A40" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B40" t="s">
         <v>27</v>
@@ -7824,16 +7834,16 @@
         <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E40" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F40" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G40" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H40">
         <v>18</v>
@@ -7851,10 +7861,10 @@
         <v>57</v>
       </c>
       <c r="M40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N40" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P40" s="14">
         <f>IF(Control!$B$7&lt;H40,0,IF(Control!$B$7&gt;=I40,1,(Control!$B$7-H40+1)/J40))</f>
@@ -7888,7 +7898,7 @@
     </row>
     <row r="41" spans="1:23">
       <c r="A41" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s">
         <v>27</v>
@@ -7897,16 +7907,16 @@
         <v>28</v>
       </c>
       <c r="D41" t="s">
+        <v>278</v>
+      </c>
+      <c r="E41" t="s">
+        <v>279</v>
+      </c>
+      <c r="F41" t="s">
         <v>280</v>
       </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>281</v>
-      </c>
-      <c r="F41" t="s">
-        <v>282</v>
-      </c>
-      <c r="G41" t="s">
-        <v>283</v>
       </c>
       <c r="H41">
         <v>22</v>
@@ -7924,10 +7934,10 @@
         <v>57</v>
       </c>
       <c r="M41" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N41" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P41" s="14">
         <f>IF(Control!$B$7&lt;H41,0,IF(Control!$B$7&gt;=I41,1,(Control!$B$7-H41+1)/J41))</f>
@@ -7961,7 +7971,7 @@
     </row>
     <row r="42" spans="1:23">
       <c r="A42" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
@@ -7970,16 +7980,16 @@
         <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E42" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F42" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G42" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H42">
         <v>22</v>
@@ -7997,10 +8007,10 @@
         <v>57</v>
       </c>
       <c r="M42" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N42" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P42" s="14">
         <f>IF(Control!$B$7&lt;H42,0,IF(Control!$B$7&gt;=I42,1,(Control!$B$7-H42+1)/J42))</f>
@@ -8034,7 +8044,7 @@
     </row>
     <row r="43" spans="1:23">
       <c r="A43" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s">
         <v>27</v>
@@ -8043,16 +8053,16 @@
         <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E43" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F43" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G43" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H43">
         <v>23</v>
@@ -8070,10 +8080,10 @@
         <v>57</v>
       </c>
       <c r="M43" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P43" s="14">
         <f>IF(Control!$B$7&lt;H43,0,IF(Control!$B$7&gt;=I43,1,(Control!$B$7-H43+1)/J43))</f>
@@ -8107,7 +8117,7 @@
     </row>
     <row r="44" spans="1:23">
       <c r="A44" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s">
         <v>27</v>
@@ -8116,16 +8126,16 @@
         <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E44" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F44" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G44" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H44">
         <v>24</v>
@@ -8143,10 +8153,10 @@
         <v>57</v>
       </c>
       <c r="M44" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N44" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P44" s="14">
         <f>IF(Control!$B$7&lt;H44,0,IF(Control!$B$7&gt;=I44,1,(Control!$B$7-H44+1)/J44))</f>
@@ -8180,7 +8190,7 @@
     </row>
     <row r="45" spans="1:23">
       <c r="A45" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
@@ -8189,13 +8199,13 @@
         <v>28</v>
       </c>
       <c r="D45" t="s">
+        <v>297</v>
+      </c>
+      <c r="E45" t="s">
+        <v>298</v>
+      </c>
+      <c r="F45" t="s">
         <v>299</v>
-      </c>
-      <c r="E45" t="s">
-        <v>300</v>
-      </c>
-      <c r="F45" t="s">
-        <v>301</v>
       </c>
       <c r="G45" t="s">
         <v>222</v>
@@ -8216,10 +8226,10 @@
         <v>57</v>
       </c>
       <c r="M45" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N45" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P45" s="14">
         <f>IF(Control!$B$7&lt;H45,0,IF(Control!$B$7&gt;=I45,1,(Control!$B$7-H45+1)/J45))</f>
@@ -8253,7 +8263,7 @@
     </row>
     <row r="46" spans="1:23">
       <c r="A46" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s">
         <v>27</v>
@@ -8262,16 +8272,16 @@
         <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E46" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F46" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G46" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H46">
         <v>23</v>
@@ -8289,10 +8299,10 @@
         <v>57</v>
       </c>
       <c r="M46" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N46" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P46" s="14">
         <f>IF(Control!$B$7&lt;H46,0,IF(Control!$B$7&gt;=I46,1,(Control!$B$7-H46+1)/J46))</f>
@@ -8326,7 +8336,7 @@
     </row>
     <row r="47" spans="1:23">
       <c r="A47" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B47" t="s">
         <v>27</v>
@@ -8335,16 +8345,16 @@
         <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E47" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F47" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H47">
         <v>24</v>
@@ -8362,10 +8372,10 @@
         <v>57</v>
       </c>
       <c r="M47" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N47" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P47" s="14">
         <f>IF(Control!$B$7&lt;H47,0,IF(Control!$B$7&gt;=I47,1,(Control!$B$7-H47+1)/J47))</f>
@@ -8399,7 +8409,7 @@
     </row>
     <row r="48" spans="1:23">
       <c r="A48" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s">
         <v>27</v>
@@ -8408,16 +8418,16 @@
         <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F48" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H48">
         <v>25</v>
@@ -8435,10 +8445,10 @@
         <v>57</v>
       </c>
       <c r="M48" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N48" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P48" s="14">
         <f>IF(Control!$B$7&lt;H48,0,IF(Control!$B$7&gt;=I48,1,(Control!$B$7-H48+1)/J48))</f>
@@ -8472,7 +8482,7 @@
     </row>
     <row r="49" spans="1:23">
       <c r="A49" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s">
         <v>27</v>
@@ -8481,16 +8491,16 @@
         <v>28</v>
       </c>
       <c r="D49" t="s">
+        <v>316</v>
+      </c>
+      <c r="E49" t="s">
+        <v>317</v>
+      </c>
+      <c r="F49" t="s">
         <v>318</v>
       </c>
-      <c r="E49" t="s">
-        <v>319</v>
-      </c>
-      <c r="F49" t="s">
-        <v>320</v>
-      </c>
       <c r="G49" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H49">
         <v>26</v>
@@ -8508,10 +8518,10 @@
         <v>57</v>
       </c>
       <c r="M49" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P49" s="14">
         <f>IF(Control!$B$7&lt;H49,0,IF(Control!$B$7&gt;=I49,1,(Control!$B$7-H49+1)/J49))</f>
@@ -8545,7 +8555,7 @@
     </row>
     <row r="50" spans="1:23">
       <c r="A50" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s">
         <v>27</v>
@@ -8554,16 +8564,16 @@
         <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E50" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F50" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G50" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H50">
         <v>26</v>
@@ -8581,10 +8591,10 @@
         <v>57</v>
       </c>
       <c r="M50" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N50" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P50" s="14">
         <f>IF(Control!$B$7&lt;H50,0,IF(Control!$B$7&gt;=I50,1,(Control!$B$7-H50+1)/J50))</f>
@@ -8618,7 +8628,7 @@
     </row>
     <row r="51" spans="1:23">
       <c r="A51" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s">
         <v>27</v>
@@ -8627,16 +8637,16 @@
         <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E51" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F51" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H51">
         <v>27</v>
@@ -8654,10 +8664,10 @@
         <v>57</v>
       </c>
       <c r="M51" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N51" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P51" s="14">
         <f>IF(Control!$B$7&lt;H51,0,IF(Control!$B$7&gt;=I51,1,(Control!$B$7-H51+1)/J51))</f>
@@ -8691,7 +8701,7 @@
     </row>
     <row r="52" spans="1:23">
       <c r="A52" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s">
         <v>27</v>
@@ -8700,16 +8710,16 @@
         <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E52" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F52" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G52" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H52">
         <v>28</v>
@@ -8727,10 +8737,10 @@
         <v>57</v>
       </c>
       <c r="M52" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N52" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P52" s="14">
         <f>IF(Control!$B$7&lt;H52,0,IF(Control!$B$7&gt;=I52,1,(Control!$B$7-H52+1)/J52))</f>
@@ -8764,7 +8774,7 @@
     </row>
     <row r="53" spans="1:23">
       <c r="A53" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s">
         <v>27</v>
@@ -8773,16 +8783,16 @@
         <v>28</v>
       </c>
       <c r="D53" t="s">
+        <v>334</v>
+      </c>
+      <c r="E53" t="s">
+        <v>335</v>
+      </c>
+      <c r="F53" t="s">
         <v>336</v>
       </c>
-      <c r="E53" t="s">
-        <v>337</v>
-      </c>
-      <c r="F53" t="s">
-        <v>338</v>
-      </c>
       <c r="G53" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H53">
         <v>29</v>
@@ -8800,10 +8810,10 @@
         <v>57</v>
       </c>
       <c r="M53" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N53" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P53" s="14">
         <f>IF(Control!$B$7&lt;H53,0,IF(Control!$B$7&gt;=I53,1,(Control!$B$7-H53+1)/J53))</f>
@@ -8837,7 +8847,7 @@
     </row>
     <row r="54" spans="1:23">
       <c r="A54" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s">
         <v>27</v>
@@ -8846,16 +8856,16 @@
         <v>28</v>
       </c>
       <c r="D54" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E54" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F54" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G54" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H54">
         <v>29</v>
@@ -8873,10 +8883,10 @@
         <v>57</v>
       </c>
       <c r="M54" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N54" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P54" s="14">
         <f>IF(Control!$B$7&lt;H54,0,IF(Control!$B$7&gt;=I54,1,(Control!$B$7-H54+1)/J54))</f>
@@ -8910,7 +8920,7 @@
     </row>
     <row r="55" spans="1:23">
       <c r="A55" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B55" t="s">
         <v>27</v>
@@ -8919,16 +8929,16 @@
         <v>28</v>
       </c>
       <c r="D55" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E55" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F55" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G55" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H55">
         <v>30</v>
@@ -8946,10 +8956,10 @@
         <v>57</v>
       </c>
       <c r="M55" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N55" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P55" s="14">
         <f>IF(Control!$B$7&lt;H55,0,IF(Control!$B$7&gt;=I55,1,(Control!$B$7-H55+1)/J55))</f>
@@ -8983,7 +8993,7 @@
     </row>
     <row r="56" spans="1:23">
       <c r="A56" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B56" t="s">
         <v>27</v>
@@ -8992,16 +9002,16 @@
         <v>28</v>
       </c>
       <c r="D56" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E56" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F56" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G56" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H56">
         <v>31</v>
@@ -9019,10 +9029,10 @@
         <v>57</v>
       </c>
       <c r="M56" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N56" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P56" s="14">
         <f>IF(Control!$B$7&lt;H56,0,IF(Control!$B$7&gt;=I56,1,(Control!$B$7-H56+1)/J56))</f>
@@ -9056,7 +9066,7 @@
     </row>
     <row r="57" spans="1:23">
       <c r="A57" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s">
         <v>27</v>
@@ -9065,16 +9075,16 @@
         <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E57" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F57" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G57" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H57">
         <v>32</v>
@@ -9092,10 +9102,10 @@
         <v>57</v>
       </c>
       <c r="M57" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N57" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O57" t="s">
         <v>29</v>
@@ -9132,7 +9142,7 @@
     </row>
     <row r="58" spans="1:23">
       <c r="A58" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B58" t="s">
         <v>27</v>
@@ -9141,16 +9151,16 @@
         <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E58" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F58" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G58" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H58">
         <v>33</v>
@@ -9168,10 +9178,10 @@
         <v>57</v>
       </c>
       <c r="M58" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="N58" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O58" t="s">
         <v>29</v>
@@ -9208,7 +9218,7 @@
     </row>
     <row r="59" spans="1:23">
       <c r="A59" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
@@ -9217,16 +9227,16 @@
         <v>31</v>
       </c>
       <c r="D59" t="s">
+        <v>363</v>
+      </c>
+      <c r="E59" t="s">
+        <v>364</v>
+      </c>
+      <c r="F59" t="s">
         <v>365</v>
       </c>
-      <c r="E59" t="s">
-        <v>366</v>
-      </c>
-      <c r="F59" t="s">
-        <v>367</v>
-      </c>
       <c r="G59" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H59">
         <v>35</v>
@@ -9244,10 +9254,10 @@
         <v>57</v>
       </c>
       <c r="M59" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N59" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P59" s="14">
         <f>IF(Control!$B$7&lt;H59,0,IF(Control!$B$7&gt;=I59,1,(Control!$B$7-H59+1)/J59))</f>
@@ -9281,7 +9291,7 @@
     </row>
     <row r="60" spans="1:23">
       <c r="A60" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B60" t="s">
         <v>30</v>
@@ -9290,16 +9300,16 @@
         <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E60" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F60" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G60" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H60">
         <v>36</v>
@@ -9317,10 +9327,10 @@
         <v>57</v>
       </c>
       <c r="M60" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N60" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P60" s="14">
         <f>IF(Control!$B$7&lt;H60,0,IF(Control!$B$7&gt;=I60,1,(Control!$B$7-H60+1)/J60))</f>
@@ -9354,7 +9364,7 @@
     </row>
     <row r="61" spans="1:23">
       <c r="A61" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s">
         <v>30</v>
@@ -9363,16 +9373,16 @@
         <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E61" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F61" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G61" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H61">
         <v>37</v>
@@ -9390,10 +9400,10 @@
         <v>57</v>
       </c>
       <c r="M61" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N61" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P61" s="14">
         <f>IF(Control!$B$7&lt;H61,0,IF(Control!$B$7&gt;=I61,1,(Control!$B$7-H61+1)/J61))</f>
@@ -9427,7 +9437,7 @@
     </row>
     <row r="62" spans="1:23">
       <c r="A62" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B62" t="s">
         <v>30</v>
@@ -9436,16 +9446,16 @@
         <v>31</v>
       </c>
       <c r="D62" t="s">
+        <v>377</v>
+      </c>
+      <c r="E62" t="s">
+        <v>378</v>
+      </c>
+      <c r="F62" t="s">
         <v>379</v>
       </c>
-      <c r="E62" t="s">
-        <v>380</v>
-      </c>
-      <c r="F62" t="s">
-        <v>381</v>
-      </c>
       <c r="G62" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H62">
         <v>38</v>
@@ -9463,10 +9473,10 @@
         <v>57</v>
       </c>
       <c r="M62" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N62" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P62" s="14">
         <f>IF(Control!$B$7&lt;H62,0,IF(Control!$B$7&gt;=I62,1,(Control!$B$7-H62+1)/J62))</f>
@@ -9500,7 +9510,7 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s">
         <v>30</v>
@@ -9509,16 +9519,16 @@
         <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E63" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F63" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G63" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H63">
         <v>39</v>
@@ -9536,10 +9546,10 @@
         <v>57</v>
       </c>
       <c r="M63" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N63" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P63" s="14">
         <f>IF(Control!$B$7&lt;H63,0,IF(Control!$B$7&gt;=I63,1,(Control!$B$7-H63+1)/J63))</f>
@@ -9573,7 +9583,7 @@
     </row>
     <row r="64" spans="1:23">
       <c r="A64" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B64" t="s">
         <v>30</v>
@@ -9582,16 +9592,16 @@
         <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E64" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F64" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G64" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H64">
         <v>40</v>
@@ -9609,10 +9619,10 @@
         <v>57</v>
       </c>
       <c r="M64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N64" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P64" s="14">
         <f>IF(Control!$B$7&lt;H64,0,IF(Control!$B$7&gt;=I64,1,(Control!$B$7-H64+1)/J64))</f>
@@ -9646,7 +9656,7 @@
     </row>
     <row r="65" spans="1:23">
       <c r="A65" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B65" t="s">
         <v>30</v>
@@ -9655,16 +9665,16 @@
         <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E65" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F65" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G65" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H65">
         <v>40</v>
@@ -9682,10 +9692,10 @@
         <v>57</v>
       </c>
       <c r="M65" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N65" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="P65" s="14">
         <f>IF(Control!$B$7&lt;H65,0,IF(Control!$B$7&gt;=I65,1,(Control!$B$7-H65+1)/J65))</f>
@@ -9719,7 +9729,7 @@
     </row>
     <row r="66" spans="1:23">
       <c r="A66" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B66" t="s">
         <v>30</v>
@@ -9728,16 +9738,16 @@
         <v>31</v>
       </c>
       <c r="D66" t="s">
+        <v>395</v>
+      </c>
+      <c r="E66" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" t="s">
         <v>397</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>398</v>
-      </c>
-      <c r="F66" t="s">
-        <v>399</v>
-      </c>
-      <c r="G66" t="s">
-        <v>400</v>
       </c>
       <c r="H66">
         <v>41</v>
@@ -9755,10 +9765,10 @@
         <v>57</v>
       </c>
       <c r="M66" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="N66" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P66" s="14">
         <f>IF(Control!$B$7&lt;H66,0,IF(Control!$B$7&gt;=I66,1,(Control!$B$7-H66+1)/J66))</f>
@@ -9792,7 +9802,7 @@
     </row>
     <row r="67" spans="1:23">
       <c r="A67" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s">
         <v>30</v>
@@ -9801,16 +9811,16 @@
         <v>31</v>
       </c>
       <c r="D67" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E67" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F67" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G67" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H67">
         <v>42</v>
@@ -9828,10 +9838,10 @@
         <v>57</v>
       </c>
       <c r="M67" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N67" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P67" s="14">
         <f>IF(Control!$B$7&lt;H67,0,IF(Control!$B$7&gt;=I67,1,(Control!$B$7-H67+1)/J67))</f>
@@ -9865,7 +9875,7 @@
     </row>
     <row r="68" spans="1:23">
       <c r="A68" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s">
         <v>30</v>
@@ -9874,16 +9884,16 @@
         <v>31</v>
       </c>
       <c r="D68" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E68" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F68" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G68" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H68">
         <v>43</v>
@@ -9901,10 +9911,10 @@
         <v>57</v>
       </c>
       <c r="M68" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N68" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P68" s="14">
         <f>IF(Control!$B$7&lt;H68,0,IF(Control!$B$7&gt;=I68,1,(Control!$B$7-H68+1)/J68))</f>
@@ -9938,7 +9948,7 @@
     </row>
     <row r="69" spans="1:23">
       <c r="A69" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s">
         <v>30</v>
@@ -9947,16 +9957,16 @@
         <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E69" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F69" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G69" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H69">
         <v>44</v>
@@ -9974,10 +9984,10 @@
         <v>57</v>
       </c>
       <c r="M69" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N69" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P69" s="14">
         <f>IF(Control!$B$7&lt;H69,0,IF(Control!$B$7&gt;=I69,1,(Control!$B$7-H69+1)/J69))</f>
@@ -10011,7 +10021,7 @@
     </row>
     <row r="70" spans="1:23">
       <c r="A70" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s">
         <v>30</v>
@@ -10020,16 +10030,16 @@
         <v>31</v>
       </c>
       <c r="D70" t="s">
+        <v>415</v>
+      </c>
+      <c r="E70" t="s">
+        <v>416</v>
+      </c>
+      <c r="F70" t="s">
         <v>417</v>
       </c>
-      <c r="E70" t="s">
-        <v>418</v>
-      </c>
-      <c r="F70" t="s">
-        <v>419</v>
-      </c>
       <c r="G70" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H70">
         <v>45</v>
@@ -10047,10 +10057,10 @@
         <v>57</v>
       </c>
       <c r="M70" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N70" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P70" s="14">
         <f>IF(Control!$B$7&lt;H70,0,IF(Control!$B$7&gt;=I70,1,(Control!$B$7-H70+1)/J70))</f>
@@ -10084,7 +10094,7 @@
     </row>
     <row r="71" spans="1:23">
       <c r="A71" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B71" t="s">
         <v>30</v>
@@ -10093,16 +10103,16 @@
         <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E71" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F71" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G71" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H71">
         <v>46</v>
@@ -10120,10 +10130,10 @@
         <v>57</v>
       </c>
       <c r="M71" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N71" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P71" s="14">
         <f>IF(Control!$B$7&lt;H71,0,IF(Control!$B$7&gt;=I71,1,(Control!$B$7-H71+1)/J71))</f>
@@ -10157,7 +10167,7 @@
     </row>
     <row r="72" spans="1:23">
       <c r="A72" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B72" t="s">
         <v>30</v>
@@ -10166,16 +10176,16 @@
         <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E72" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F72" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G72" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H72">
         <v>46</v>
@@ -10193,10 +10203,10 @@
         <v>57</v>
       </c>
       <c r="M72" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N72" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P72" s="14">
         <f>IF(Control!$B$7&lt;H72,0,IF(Control!$B$7&gt;=I72,1,(Control!$B$7-H72+1)/J72))</f>
@@ -10230,7 +10240,7 @@
     </row>
     <row r="73" spans="1:23">
       <c r="A73" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s">
         <v>30</v>
@@ -10239,16 +10249,16 @@
         <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E73" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F73" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G73" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H73">
         <v>47</v>
@@ -10266,10 +10276,10 @@
         <v>57</v>
       </c>
       <c r="M73" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="N73" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="P73" s="14">
         <f>IF(Control!$B$7&lt;H73,0,IF(Control!$B$7&gt;=I73,1,(Control!$B$7-H73+1)/J73))</f>
@@ -10303,7 +10313,7 @@
     </row>
     <row r="74" spans="1:23">
       <c r="A74" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s">
         <v>30</v>
@@ -10312,16 +10322,16 @@
         <v>31</v>
       </c>
       <c r="D74" t="s">
+        <v>435</v>
+      </c>
+      <c r="E74" t="s">
+        <v>436</v>
+      </c>
+      <c r="F74" t="s">
         <v>437</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>438</v>
-      </c>
-      <c r="F74" t="s">
-        <v>439</v>
-      </c>
-      <c r="G74" t="s">
-        <v>440</v>
       </c>
       <c r="H74">
         <v>38</v>
@@ -10339,10 +10349,10 @@
         <v>57</v>
       </c>
       <c r="M74" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N74" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P74" s="14">
         <f>IF(Control!$B$7&lt;H74,0,IF(Control!$B$7&gt;=I74,1,(Control!$B$7-H74+1)/J74))</f>
@@ -10376,7 +10386,7 @@
     </row>
     <row r="75" spans="1:23">
       <c r="A75" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B75" t="s">
         <v>30</v>
@@ -10385,16 +10395,16 @@
         <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E75" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F75" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G75" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H75">
         <v>39</v>
@@ -10412,10 +10422,10 @@
         <v>57</v>
       </c>
       <c r="M75" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N75" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P75" s="14">
         <f>IF(Control!$B$7&lt;H75,0,IF(Control!$B$7&gt;=I75,1,(Control!$B$7-H75+1)/J75))</f>
@@ -10449,7 +10459,7 @@
     </row>
     <row r="76" spans="1:23">
       <c r="A76" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s">
         <v>30</v>
@@ -10458,16 +10468,16 @@
         <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E76" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F76" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G76" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H76">
         <v>41</v>
@@ -10485,10 +10495,10 @@
         <v>57</v>
       </c>
       <c r="M76" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N76" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P76" s="14">
         <f>IF(Control!$B$7&lt;H76,0,IF(Control!$B$7&gt;=I76,1,(Control!$B$7-H76+1)/J76))</f>
@@ -10522,7 +10532,7 @@
     </row>
     <row r="77" spans="1:23">
       <c r="A77" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s">
         <v>30</v>
@@ -10531,16 +10541,16 @@
         <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E77" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F77" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G77" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H77">
         <v>42</v>
@@ -10558,10 +10568,10 @@
         <v>57</v>
       </c>
       <c r="M77" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N77" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P77" s="14">
         <f>IF(Control!$B$7&lt;H77,0,IF(Control!$B$7&gt;=I77,1,(Control!$B$7-H77+1)/J77))</f>
@@ -10595,7 +10605,7 @@
     </row>
     <row r="78" spans="1:23">
       <c r="A78" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s">
         <v>30</v>
@@ -10604,16 +10614,16 @@
         <v>31</v>
       </c>
       <c r="D78" t="s">
+        <v>456</v>
+      </c>
+      <c r="E78" t="s">
+        <v>457</v>
+      </c>
+      <c r="F78" t="s">
         <v>458</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>459</v>
-      </c>
-      <c r="F78" t="s">
-        <v>460</v>
-      </c>
-      <c r="G78" t="s">
-        <v>461</v>
       </c>
       <c r="H78">
         <v>48</v>
@@ -10631,10 +10641,10 @@
         <v>57</v>
       </c>
       <c r="M78" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N78" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P78" s="14">
         <f>IF(Control!$B$7&lt;H78,0,IF(Control!$B$7&gt;=I78,1,(Control!$B$7-H78+1)/J78))</f>
@@ -10668,7 +10678,7 @@
     </row>
     <row r="79" spans="1:23">
       <c r="A79" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s">
         <v>30</v>
@@ -10677,16 +10687,16 @@
         <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E79" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F79" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G79" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H79">
         <v>49</v>
@@ -10704,10 +10714,10 @@
         <v>57</v>
       </c>
       <c r="M79" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N79" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P79" s="14">
         <f>IF(Control!$B$7&lt;H79,0,IF(Control!$B$7&gt;=I79,1,(Control!$B$7-H79+1)/J79))</f>
@@ -10741,7 +10751,7 @@
     </row>
     <row r="80" spans="1:23">
       <c r="A80" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B80" t="s">
         <v>30</v>
@@ -10750,16 +10760,16 @@
         <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E80" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F80" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G80" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H80">
         <v>50</v>
@@ -10777,10 +10787,10 @@
         <v>57</v>
       </c>
       <c r="M80" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N80" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P80" s="14">
         <f>IF(Control!$B$7&lt;H80,0,IF(Control!$B$7&gt;=I80,1,(Control!$B$7-H80+1)/J80))</f>
@@ -10814,7 +10824,7 @@
     </row>
     <row r="81" spans="1:23">
       <c r="A81" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B81" t="s">
         <v>30</v>
@@ -10823,16 +10833,16 @@
         <v>31</v>
       </c>
       <c r="D81" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E81" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F81" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G81" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H81">
         <v>50</v>
@@ -10850,10 +10860,10 @@
         <v>57</v>
       </c>
       <c r="M81" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N81" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P81" s="14">
         <f>IF(Control!$B$7&lt;H81,0,IF(Control!$B$7&gt;=I81,1,(Control!$B$7-H81+1)/J81))</f>
@@ -10887,7 +10897,7 @@
     </row>
     <row r="82" spans="1:23">
       <c r="A82" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s">
         <v>30</v>
@@ -10896,16 +10906,16 @@
         <v>31</v>
       </c>
       <c r="D82" t="s">
+        <v>475</v>
+      </c>
+      <c r="E82" t="s">
+        <v>476</v>
+      </c>
+      <c r="F82" t="s">
         <v>477</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>478</v>
-      </c>
-      <c r="F82" t="s">
-        <v>479</v>
-      </c>
-      <c r="G82" t="s">
-        <v>480</v>
       </c>
       <c r="H82">
         <v>51</v>
@@ -10923,10 +10933,10 @@
         <v>57</v>
       </c>
       <c r="M82" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="N82" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P82" s="14">
         <f>IF(Control!$B$7&lt;H82,0,IF(Control!$B$7&gt;=I82,1,(Control!$B$7-H82+1)/J82))</f>
@@ -10960,7 +10970,7 @@
     </row>
     <row r="83" spans="1:23">
       <c r="A83" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s">
         <v>30</v>
@@ -10969,16 +10979,16 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E83" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F83" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G83" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H83">
         <v>51</v>
@@ -10996,10 +11006,10 @@
         <v>57</v>
       </c>
       <c r="M83" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="N83" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P83" s="14">
         <f>IF(Control!$B$7&lt;H83,0,IF(Control!$B$7&gt;=I83,1,(Control!$B$7-H83+1)/J83))</f>
@@ -11033,7 +11043,7 @@
     </row>
     <row r="84" spans="1:23">
       <c r="A84" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s">
         <v>30</v>
@@ -11042,16 +11052,16 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E84" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F84" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G84" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H84">
         <v>53</v>
@@ -11069,10 +11079,10 @@
         <v>57</v>
       </c>
       <c r="M84" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="N84" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P84" s="14">
         <f>IF(Control!$B$7&lt;H84,0,IF(Control!$B$7&gt;=I84,1,(Control!$B$7-H84+1)/J84))</f>
@@ -11106,7 +11116,7 @@
     </row>
     <row r="85" spans="1:23">
       <c r="A85" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s">
         <v>30</v>
@@ -11115,16 +11125,16 @@
         <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E85" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F85" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G85" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H85">
         <v>54</v>
@@ -11142,10 +11152,10 @@
         <v>57</v>
       </c>
       <c r="M85" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N85" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P85" s="14">
         <f>IF(Control!$B$7&lt;H85,0,IF(Control!$B$7&gt;=I85,1,(Control!$B$7-H85+1)/J85))</f>
@@ -11179,7 +11189,7 @@
     </row>
     <row r="86" spans="1:23">
       <c r="A86" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B86" t="s">
         <v>30</v>
@@ -11188,16 +11198,16 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
+        <v>496</v>
+      </c>
+      <c r="E86" t="s">
+        <v>497</v>
+      </c>
+      <c r="F86" t="s">
         <v>498</v>
       </c>
-      <c r="E86" t="s">
-        <v>499</v>
-      </c>
-      <c r="F86" t="s">
-        <v>500</v>
-      </c>
       <c r="G86" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H86">
         <v>35</v>
@@ -11215,10 +11225,10 @@
         <v>57</v>
       </c>
       <c r="M86" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N86" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P86" s="14">
         <f>IF(Control!$B$7&lt;H86,0,IF(Control!$B$7&gt;=I86,1,(Control!$B$7-H86+1)/J86))</f>
@@ -11252,7 +11262,7 @@
     </row>
     <row r="87" spans="1:23">
       <c r="A87" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B87" t="s">
         <v>30</v>
@@ -11261,16 +11271,16 @@
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E87" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F87" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G87" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H87">
         <v>43</v>
@@ -11288,10 +11298,10 @@
         <v>57</v>
       </c>
       <c r="M87" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N87" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="P87" s="14">
         <f>IF(Control!$B$7&lt;H87,0,IF(Control!$B$7&gt;=I87,1,(Control!$B$7-H87+1)/J87))</f>
@@ -11325,7 +11335,7 @@
     </row>
     <row r="88" spans="1:23">
       <c r="A88" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B88" t="s">
         <v>30</v>
@@ -11334,16 +11344,16 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E88" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F88" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G88" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H88">
         <v>53</v>
@@ -11361,10 +11371,10 @@
         <v>57</v>
       </c>
       <c r="M88" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N88" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="P88" s="14">
         <f>IF(Control!$B$7&lt;H88,0,IF(Control!$B$7&gt;=I88,1,(Control!$B$7-H88+1)/J88))</f>
@@ -11398,7 +11408,7 @@
     </row>
     <row r="89" spans="1:23">
       <c r="A89" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B89" t="s">
         <v>30</v>
@@ -11407,16 +11417,16 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E89" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F89" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G89" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H89">
         <v>54</v>
@@ -11434,10 +11444,10 @@
         <v>57</v>
       </c>
       <c r="M89" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N89" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="P89" s="14">
         <f>IF(Control!$B$7&lt;H89,0,IF(Control!$B$7&gt;=I89,1,(Control!$B$7-H89+1)/J89))</f>
@@ -11471,7 +11481,7 @@
     </row>
     <row r="90" spans="1:23">
       <c r="A90" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B90" t="s">
         <v>30</v>
@@ -11480,16 +11490,16 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E90" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F90" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G90" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H90">
         <v>55</v>
@@ -11507,10 +11517,10 @@
         <v>57</v>
       </c>
       <c r="M90" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N90" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="O90" t="s">
         <v>32</v>
@@ -11547,7 +11557,7 @@
     </row>
     <row r="91" spans="1:23">
       <c r="A91" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s">
         <v>30</v>
@@ -11556,16 +11566,16 @@
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E91" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F91" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G91" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H91">
         <v>56</v>
@@ -11583,10 +11593,10 @@
         <v>57</v>
       </c>
       <c r="M91" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="N91" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="O91" t="s">
         <v>32</v>
@@ -11623,7 +11633,7 @@
     </row>
     <row r="92" spans="1:23">
       <c r="A92" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B92" t="s">
         <v>33</v>
@@ -11632,16 +11642,16 @@
         <v>34</v>
       </c>
       <c r="D92" t="s">
+        <v>524</v>
+      </c>
+      <c r="E92" t="s">
+        <v>525</v>
+      </c>
+      <c r="F92" t="s">
         <v>526</v>
       </c>
-      <c r="E92" t="s">
-        <v>527</v>
-      </c>
-      <c r="F92" t="s">
-        <v>528</v>
-      </c>
       <c r="G92" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H92">
         <v>57</v>
@@ -11659,10 +11669,10 @@
         <v>57</v>
       </c>
       <c r="M92" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="N92" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P92" s="14">
         <f>IF(Control!$B$7&lt;H92,0,IF(Control!$B$7&gt;=I92,1,(Control!$B$7-H92+1)/J92))</f>
@@ -11696,7 +11706,7 @@
     </row>
     <row r="93" spans="1:23">
       <c r="A93" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B93" t="s">
         <v>33</v>
@@ -11705,16 +11715,16 @@
         <v>34</v>
       </c>
       <c r="D93" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E93" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F93" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G93" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H93">
         <v>58</v>
@@ -11732,10 +11742,10 @@
         <v>57</v>
       </c>
       <c r="M93" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N93" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P93" s="14">
         <f>IF(Control!$B$7&lt;H93,0,IF(Control!$B$7&gt;=I93,1,(Control!$B$7-H93+1)/J93))</f>
@@ -11769,7 +11779,7 @@
     </row>
     <row r="94" spans="1:23">
       <c r="A94" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B94" t="s">
         <v>33</v>
@@ -11778,16 +11788,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E94" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F94" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G94" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H94">
         <v>58</v>
@@ -11805,10 +11815,10 @@
         <v>57</v>
       </c>
       <c r="M94" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N94" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P94" s="14">
         <f>IF(Control!$B$7&lt;H94,0,IF(Control!$B$7&gt;=I94,1,(Control!$B$7-H94+1)/J94))</f>
@@ -11842,7 +11852,7 @@
     </row>
     <row r="95" spans="1:23">
       <c r="A95" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s">
         <v>33</v>
@@ -11851,16 +11861,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="s">
+        <v>538</v>
+      </c>
+      <c r="E95" t="s">
+        <v>539</v>
+      </c>
+      <c r="F95" t="s">
         <v>540</v>
       </c>
-      <c r="E95" t="s">
-        <v>541</v>
-      </c>
-      <c r="F95" t="s">
-        <v>542</v>
-      </c>
       <c r="G95" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H95">
         <v>57</v>
@@ -11878,10 +11888,10 @@
         <v>57</v>
       </c>
       <c r="M95" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N95" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="P95" s="14">
         <f>IF(Control!$B$7&lt;H95,0,IF(Control!$B$7&gt;=I95,1,(Control!$B$7-H95+1)/J95))</f>
@@ -11915,7 +11925,7 @@
     </row>
     <row r="96" spans="1:23">
       <c r="A96" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s">
         <v>33</v>
@@ -11924,16 +11934,16 @@
         <v>34</v>
       </c>
       <c r="D96" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E96" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F96" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G96" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H96">
         <v>59</v>
@@ -11951,10 +11961,10 @@
         <v>57</v>
       </c>
       <c r="M96" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="N96" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="P96" s="14">
         <f>IF(Control!$B$7&lt;H96,0,IF(Control!$B$7&gt;=I96,1,(Control!$B$7-H96+1)/J96))</f>
@@ -11988,7 +11998,7 @@
     </row>
     <row r="97" spans="1:23">
       <c r="A97" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s">
         <v>33</v>
@@ -11997,16 +12007,16 @@
         <v>34</v>
       </c>
       <c r="D97" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E97" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F97" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G97" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H97">
         <v>60</v>
@@ -12024,10 +12034,10 @@
         <v>57</v>
       </c>
       <c r="M97" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="N97" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="P97" s="14">
         <f>IF(Control!$B$7&lt;H97,0,IF(Control!$B$7&gt;=I97,1,(Control!$B$7-H97+1)/J97))</f>
@@ -12061,7 +12071,7 @@
     </row>
     <row r="98" spans="1:23">
       <c r="A98" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B98" t="s">
         <v>33</v>
@@ -12070,16 +12080,16 @@
         <v>34</v>
       </c>
       <c r="D98" t="s">
+        <v>552</v>
+      </c>
+      <c r="E98" t="s">
+        <v>553</v>
+      </c>
+      <c r="F98" t="s">
         <v>554</v>
       </c>
-      <c r="E98" t="s">
-        <v>555</v>
-      </c>
-      <c r="F98" t="s">
-        <v>556</v>
-      </c>
       <c r="G98" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H98">
         <v>61</v>
@@ -12097,10 +12107,10 @@
         <v>57</v>
       </c>
       <c r="M98" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="N98" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="P98" s="14">
         <f>IF(Control!$B$7&lt;H98,0,IF(Control!$B$7&gt;=I98,1,(Control!$B$7-H98+1)/J98))</f>
@@ -12134,7 +12144,7 @@
     </row>
     <row r="99" spans="1:23">
       <c r="A99" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B99" t="s">
         <v>33</v>
@@ -12143,16 +12153,16 @@
         <v>34</v>
       </c>
       <c r="D99" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E99" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F99" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G99" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H99">
         <v>62</v>
@@ -12170,10 +12180,10 @@
         <v>57</v>
       </c>
       <c r="M99" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="N99" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P99" s="14">
         <f>IF(Control!$B$7&lt;H99,0,IF(Control!$B$7&gt;=I99,1,(Control!$B$7-H99+1)/J99))</f>
@@ -12207,7 +12217,7 @@
     </row>
     <row r="100" spans="1:23">
       <c r="A100" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B100" t="s">
         <v>33</v>
@@ -12216,16 +12226,16 @@
         <v>34</v>
       </c>
       <c r="D100" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E100" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F100" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G100" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H100">
         <v>62</v>
@@ -12243,10 +12253,10 @@
         <v>57</v>
       </c>
       <c r="M100" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N100" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="P100" s="14">
         <f>IF(Control!$B$7&lt;H100,0,IF(Control!$B$7&gt;=I100,1,(Control!$B$7-H100+1)/J100))</f>
@@ -12280,7 +12290,7 @@
     </row>
     <row r="101" spans="1:23">
       <c r="A101" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B101" t="s">
         <v>33</v>
@@ -12289,16 +12299,16 @@
         <v>34</v>
       </c>
       <c r="D101" t="s">
+        <v>566</v>
+      </c>
+      <c r="E101" t="s">
+        <v>567</v>
+      </c>
+      <c r="F101" t="s">
         <v>568</v>
       </c>
-      <c r="E101" t="s">
-        <v>569</v>
-      </c>
-      <c r="F101" t="s">
-        <v>570</v>
-      </c>
       <c r="G101" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H101">
         <v>63</v>
@@ -12316,10 +12326,10 @@
         <v>57</v>
       </c>
       <c r="M101" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N101" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="P101" s="14">
         <f>IF(Control!$B$7&lt;H101,0,IF(Control!$B$7&gt;=I101,1,(Control!$B$7-H101+1)/J101))</f>
@@ -12353,7 +12363,7 @@
     </row>
     <row r="102" spans="1:23">
       <c r="A102" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B102" t="s">
         <v>33</v>
@@ -12362,16 +12372,16 @@
         <v>34</v>
       </c>
       <c r="D102" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E102" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F102" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G102" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H102">
         <v>64</v>
@@ -12389,10 +12399,10 @@
         <v>57</v>
       </c>
       <c r="M102" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="N102" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="P102" s="14">
         <f>IF(Control!$B$7&lt;H102,0,IF(Control!$B$7&gt;=I102,1,(Control!$B$7-H102+1)/J102))</f>
@@ -12426,7 +12436,7 @@
     </row>
     <row r="103" spans="1:23">
       <c r="A103" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B103" t="s">
         <v>33</v>
@@ -12435,16 +12445,16 @@
         <v>34</v>
       </c>
       <c r="D103" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E103" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F103" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G103" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H103">
         <v>65</v>
@@ -12462,10 +12472,10 @@
         <v>57</v>
       </c>
       <c r="M103" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N103" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="P103" s="14">
         <f>IF(Control!$B$7&lt;H103,0,IF(Control!$B$7&gt;=I103,1,(Control!$B$7-H103+1)/J103))</f>
@@ -12499,7 +12509,7 @@
     </row>
     <row r="104" spans="1:23">
       <c r="A104" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B104" t="s">
         <v>33</v>
@@ -12508,16 +12518,16 @@
         <v>34</v>
       </c>
       <c r="D104" t="s">
+        <v>580</v>
+      </c>
+      <c r="E104" t="s">
+        <v>581</v>
+      </c>
+      <c r="F104" t="s">
         <v>582</v>
       </c>
-      <c r="E104" t="s">
-        <v>583</v>
-      </c>
-      <c r="F104" t="s">
-        <v>584</v>
-      </c>
       <c r="G104" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H104">
         <v>65</v>
@@ -12535,10 +12545,10 @@
         <v>57</v>
       </c>
       <c r="M104" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N104" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P104" s="14">
         <f>IF(Control!$B$7&lt;H104,0,IF(Control!$B$7&gt;=I104,1,(Control!$B$7-H104+1)/J104))</f>
@@ -12572,7 +12582,7 @@
     </row>
     <row r="105" spans="1:23">
       <c r="A105" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B105" t="s">
         <v>33</v>
@@ -12581,16 +12591,16 @@
         <v>34</v>
       </c>
       <c r="D105" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E105" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F105" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G105" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H105">
         <v>66</v>
@@ -12608,10 +12618,10 @@
         <v>57</v>
       </c>
       <c r="M105" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="N105" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P105" s="14">
         <f>IF(Control!$B$7&lt;H105,0,IF(Control!$B$7&gt;=I105,1,(Control!$B$7-H105+1)/J105))</f>
@@ -12645,7 +12655,7 @@
     </row>
     <row r="106" spans="1:23">
       <c r="A106" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B106" t="s">
         <v>33</v>
@@ -12654,16 +12664,16 @@
         <v>34</v>
       </c>
       <c r="D106" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E106" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F106" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G106" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H106">
         <v>67</v>
@@ -12681,10 +12691,10 @@
         <v>57</v>
       </c>
       <c r="M106" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N106" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="P106" s="14">
         <f>IF(Control!$B$7&lt;H106,0,IF(Control!$B$7&gt;=I106,1,(Control!$B$7-H106+1)/J106))</f>
@@ -12718,7 +12728,7 @@
     </row>
     <row r="107" spans="1:23">
       <c r="A107" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B107" t="s">
         <v>33</v>
@@ -12727,16 +12737,16 @@
         <v>34</v>
       </c>
       <c r="D107" t="s">
+        <v>594</v>
+      </c>
+      <c r="E107" t="s">
+        <v>595</v>
+      </c>
+      <c r="F107" t="s">
         <v>596</v>
       </c>
-      <c r="E107" t="s">
-        <v>597</v>
-      </c>
-      <c r="F107" t="s">
-        <v>598</v>
-      </c>
       <c r="G107" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H107">
         <v>68</v>
@@ -12754,10 +12764,10 @@
         <v>57</v>
       </c>
       <c r="M107" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N107" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="P107" s="14">
         <f>IF(Control!$B$7&lt;H107,0,IF(Control!$B$7&gt;=I107,1,(Control!$B$7-H107+1)/J107))</f>
@@ -12791,7 +12801,7 @@
     </row>
     <row r="108" spans="1:23">
       <c r="A108" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B108" t="s">
         <v>33</v>
@@ -12800,16 +12810,16 @@
         <v>34</v>
       </c>
       <c r="D108" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E108" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F108" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G108" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H108">
         <v>68</v>
@@ -12827,10 +12837,10 @@
         <v>57</v>
       </c>
       <c r="M108" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N108" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P108" s="14">
         <f>IF(Control!$B$7&lt;H108,0,IF(Control!$B$7&gt;=I108,1,(Control!$B$7-H108+1)/J108))</f>
@@ -12864,7 +12874,7 @@
     </row>
     <row r="109" spans="1:23">
       <c r="A109" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B109" t="s">
         <v>33</v>
@@ -12873,16 +12883,16 @@
         <v>34</v>
       </c>
       <c r="D109" t="s">
+        <v>604</v>
+      </c>
+      <c r="E109" t="s">
+        <v>605</v>
+      </c>
+      <c r="F109" t="s">
         <v>606</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>607</v>
-      </c>
-      <c r="F109" t="s">
-        <v>608</v>
-      </c>
-      <c r="G109" t="s">
-        <v>609</v>
       </c>
       <c r="H109">
         <v>69</v>
@@ -12900,10 +12910,10 @@
         <v>57</v>
       </c>
       <c r="M109" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="N109" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="P109" s="14">
         <f>IF(Control!$B$7&lt;H109,0,IF(Control!$B$7&gt;=I109,1,(Control!$B$7-H109+1)/J109))</f>
@@ -12937,7 +12947,7 @@
     </row>
     <row r="110" spans="1:23">
       <c r="A110" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B110" t="s">
         <v>33</v>
@@ -12946,16 +12956,16 @@
         <v>34</v>
       </c>
       <c r="D110" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E110" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F110" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G110" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H110">
         <v>69</v>
@@ -12973,10 +12983,10 @@
         <v>57</v>
       </c>
       <c r="M110" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="N110" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="P110" s="14">
         <f>IF(Control!$B$7&lt;H110,0,IF(Control!$B$7&gt;=I110,1,(Control!$B$7-H110+1)/J110))</f>
@@ -13010,7 +13020,7 @@
     </row>
     <row r="111" spans="1:23">
       <c r="A111" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B111" t="s">
         <v>33</v>
@@ -13019,16 +13029,16 @@
         <v>34</v>
       </c>
       <c r="D111" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E111" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F111" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G111" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H111">
         <v>70</v>
@@ -13046,10 +13056,10 @@
         <v>57</v>
       </c>
       <c r="M111" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="N111" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="O111" t="s">
         <v>35</v>
@@ -13086,7 +13096,7 @@
     </row>
     <row r="112" spans="1:23">
       <c r="A112" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B112" t="s">
         <v>36</v>
@@ -13095,16 +13105,16 @@
         <v>37</v>
       </c>
       <c r="D112" t="s">
+        <v>620</v>
+      </c>
+      <c r="E112" t="s">
+        <v>621</v>
+      </c>
+      <c r="F112" t="s">
         <v>622</v>
       </c>
-      <c r="E112" t="s">
-        <v>623</v>
-      </c>
-      <c r="F112" t="s">
-        <v>624</v>
-      </c>
       <c r="G112" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H112">
         <v>71</v>
@@ -13122,10 +13132,10 @@
         <v>57</v>
       </c>
       <c r="M112" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="N112" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="P112" s="14">
         <f>IF(Control!$B$7&lt;H112,0,IF(Control!$B$7&gt;=I112,1,(Control!$B$7-H112+1)/J112))</f>
@@ -13159,7 +13169,7 @@
     </row>
     <row r="113" spans="1:23">
       <c r="A113" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B113" t="s">
         <v>36</v>
@@ -13168,16 +13178,16 @@
         <v>37</v>
       </c>
       <c r="D113" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E113" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F113" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G113" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H113">
         <v>72</v>
@@ -13195,10 +13205,10 @@
         <v>57</v>
       </c>
       <c r="M113" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="N113" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="P113" s="14">
         <f>IF(Control!$B$7&lt;H113,0,IF(Control!$B$7&gt;=I113,1,(Control!$B$7-H113+1)/J113))</f>
@@ -13232,7 +13242,7 @@
     </row>
     <row r="114" spans="1:23">
       <c r="A114" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B114" t="s">
         <v>36</v>
@@ -13241,16 +13251,16 @@
         <v>37</v>
       </c>
       <c r="D114" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E114" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F114" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G114" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H114">
         <v>73</v>
@@ -13268,10 +13278,10 @@
         <v>57</v>
       </c>
       <c r="M114" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="N114" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="P114" s="14">
         <f>IF(Control!$B$7&lt;H114,0,IF(Control!$B$7&gt;=I114,1,(Control!$B$7-H114+1)/J114))</f>
@@ -13305,7 +13315,7 @@
     </row>
     <row r="115" spans="1:23">
       <c r="A115" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B115" t="s">
         <v>36</v>
@@ -13314,16 +13324,16 @@
         <v>37</v>
       </c>
       <c r="D115" t="s">
+        <v>634</v>
+      </c>
+      <c r="E115" t="s">
+        <v>635</v>
+      </c>
+      <c r="F115" t="s">
         <v>636</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>637</v>
-      </c>
-      <c r="F115" t="s">
-        <v>638</v>
-      </c>
-      <c r="G115" t="s">
-        <v>639</v>
       </c>
       <c r="H115">
         <v>73</v>
@@ -13341,10 +13351,10 @@
         <v>57</v>
       </c>
       <c r="M115" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="N115" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="P115" s="14">
         <f>IF(Control!$B$7&lt;H115,0,IF(Control!$B$7&gt;=I115,1,(Control!$B$7-H115+1)/J115))</f>
@@ -13378,7 +13388,7 @@
     </row>
     <row r="116" spans="1:23">
       <c r="A116" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B116" t="s">
         <v>36</v>
@@ -13387,16 +13397,16 @@
         <v>37</v>
       </c>
       <c r="D116" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E116" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F116" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G116" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H116">
         <v>74</v>
@@ -13414,10 +13424,10 @@
         <v>57</v>
       </c>
       <c r="M116" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="N116" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="P116" s="14">
         <f>IF(Control!$B$7&lt;H116,0,IF(Control!$B$7&gt;=I116,1,(Control!$B$7-H116+1)/J116))</f>
@@ -13451,7 +13461,7 @@
     </row>
     <row r="117" spans="1:23">
       <c r="A117" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B117" t="s">
         <v>36</v>
@@ -13460,16 +13470,16 @@
         <v>37</v>
       </c>
       <c r="D117" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E117" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F117" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G117" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H117">
         <v>74</v>
@@ -13487,10 +13497,10 @@
         <v>57</v>
       </c>
       <c r="M117" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="N117" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="P117" s="14">
         <f>IF(Control!$B$7&lt;H117,0,IF(Control!$B$7&gt;=I117,1,(Control!$B$7-H117+1)/J117))</f>
@@ -13524,7 +13534,7 @@
     </row>
     <row r="118" spans="1:23">
       <c r="A118" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B118" t="s">
         <v>36</v>
@@ -13533,16 +13543,16 @@
         <v>37</v>
       </c>
       <c r="D118" t="s">
+        <v>649</v>
+      </c>
+      <c r="E118" t="s">
+        <v>650</v>
+      </c>
+      <c r="F118" t="s">
         <v>651</v>
       </c>
-      <c r="E118" t="s">
-        <v>652</v>
-      </c>
-      <c r="F118" t="s">
-        <v>653</v>
-      </c>
       <c r="G118" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H118">
         <v>75</v>
@@ -13560,10 +13570,10 @@
         <v>57</v>
       </c>
       <c r="M118" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="N118" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="P118" s="14">
         <f>IF(Control!$B$7&lt;H118,0,IF(Control!$B$7&gt;=I118,1,(Control!$B$7-H118+1)/J118))</f>
@@ -13597,7 +13607,7 @@
     </row>
     <row r="119" spans="1:23">
       <c r="A119" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B119" t="s">
         <v>36</v>
@@ -13606,16 +13616,16 @@
         <v>37</v>
       </c>
       <c r="D119" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E119" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F119" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G119" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H119">
         <v>75</v>
@@ -13633,10 +13643,10 @@
         <v>57</v>
       </c>
       <c r="M119" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="N119" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="P119" s="14">
         <f>IF(Control!$B$7&lt;H119,0,IF(Control!$B$7&gt;=I119,1,(Control!$B$7-H119+1)/J119))</f>
@@ -13670,7 +13680,7 @@
     </row>
     <row r="120" spans="1:23">
       <c r="A120" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B120" t="s">
         <v>36</v>
@@ -13679,16 +13689,16 @@
         <v>37</v>
       </c>
       <c r="D120" t="s">
+        <v>659</v>
+      </c>
+      <c r="E120" t="s">
+        <v>660</v>
+      </c>
+      <c r="F120" t="s">
         <v>661</v>
       </c>
-      <c r="E120" t="s">
-        <v>662</v>
-      </c>
-      <c r="F120" t="s">
-        <v>663</v>
-      </c>
       <c r="G120" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H120">
         <v>76</v>
@@ -13706,10 +13716,10 @@
         <v>57</v>
       </c>
       <c r="M120" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="N120" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="P120" s="14">
         <f>IF(Control!$B$7&lt;H120,0,IF(Control!$B$7&gt;=I120,1,(Control!$B$7-H120+1)/J120))</f>
@@ -13743,7 +13753,7 @@
     </row>
     <row r="121" spans="1:23">
       <c r="A121" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B121" t="s">
         <v>36</v>
@@ -13752,16 +13762,16 @@
         <v>37</v>
       </c>
       <c r="D121" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E121" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F121" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G121" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H121">
         <v>77</v>
@@ -13779,10 +13789,10 @@
         <v>57</v>
       </c>
       <c r="M121" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N121" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="P121" s="14">
         <f>IF(Control!$B$7&lt;H121,0,IF(Control!$B$7&gt;=I121,1,(Control!$B$7-H121+1)/J121))</f>
@@ -13816,7 +13826,7 @@
     </row>
     <row r="122" spans="1:23">
       <c r="A122" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B122" t="s">
         <v>36</v>
@@ -13825,16 +13835,16 @@
         <v>37</v>
       </c>
       <c r="D122" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E122" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F122" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G122" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H122">
         <v>78</v>
@@ -13852,10 +13862,10 @@
         <v>57</v>
       </c>
       <c r="M122" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="N122" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="O122" t="s">
         <v>38</v>
@@ -13892,7 +13902,7 @@
     </row>
     <row r="123" spans="1:23">
       <c r="A123" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B123" t="s">
         <v>36</v>
@@ -13901,16 +13911,16 @@
         <v>37</v>
       </c>
       <c r="D123" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E123" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F123" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G123" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H123">
         <v>78</v>
@@ -13928,10 +13938,10 @@
         <v>57</v>
       </c>
       <c r="M123" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="N123" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="O123" t="s">
         <v>38</v>
@@ -13968,7 +13978,7 @@
     </row>
     <row r="124" spans="1:23">
       <c r="A124" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B124" t="s">
         <v>39</v>
@@ -13977,16 +13987,16 @@
         <v>40</v>
       </c>
       <c r="D124" t="s">
+        <v>677</v>
+      </c>
+      <c r="E124" t="s">
+        <v>678</v>
+      </c>
+      <c r="F124" t="s">
         <v>679</v>
       </c>
-      <c r="E124" t="s">
-        <v>680</v>
-      </c>
-      <c r="F124" t="s">
-        <v>681</v>
-      </c>
       <c r="G124" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H124">
         <v>79</v>
@@ -14004,10 +14014,10 @@
         <v>57</v>
       </c>
       <c r="M124" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="N124" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="P124" s="14">
         <f>IF(Control!$B$7&lt;H124,0,IF(Control!$B$7&gt;=I124,1,(Control!$B$7-H124+1)/J124))</f>
@@ -14041,7 +14051,7 @@
     </row>
     <row r="125" spans="1:23">
       <c r="A125" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B125" t="s">
         <v>39</v>
@@ -14050,16 +14060,16 @@
         <v>40</v>
       </c>
       <c r="D125" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E125" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F125" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G125" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H125">
         <v>80</v>
@@ -14077,10 +14087,10 @@
         <v>57</v>
       </c>
       <c r="M125" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="N125" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="P125" s="14">
         <f>IF(Control!$B$7&lt;H125,0,IF(Control!$B$7&gt;=I125,1,(Control!$B$7-H125+1)/J125))</f>
@@ -14114,7 +14124,7 @@
     </row>
     <row r="126" spans="1:23">
       <c r="A126" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B126" t="s">
         <v>39</v>
@@ -14123,16 +14133,16 @@
         <v>40</v>
       </c>
       <c r="D126" t="s">
+        <v>687</v>
+      </c>
+      <c r="E126" t="s">
+        <v>688</v>
+      </c>
+      <c r="F126" t="s">
         <v>689</v>
       </c>
-      <c r="E126" t="s">
-        <v>690</v>
-      </c>
-      <c r="F126" t="s">
-        <v>691</v>
-      </c>
       <c r="G126" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H126">
         <v>79</v>
@@ -14150,10 +14160,10 @@
         <v>57</v>
       </c>
       <c r="M126" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="N126" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="P126" s="14">
         <f>IF(Control!$B$7&lt;H126,0,IF(Control!$B$7&gt;=I126,1,(Control!$B$7-H126+1)/J126))</f>
@@ -14187,7 +14197,7 @@
     </row>
     <row r="127" spans="1:23">
       <c r="A127" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B127" t="s">
         <v>39</v>
@@ -14196,16 +14206,16 @@
         <v>40</v>
       </c>
       <c r="D127" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E127" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F127" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G127" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H127">
         <v>80</v>
@@ -14223,10 +14233,10 @@
         <v>57</v>
       </c>
       <c r="M127" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="N127" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="P127" s="14">
         <f>IF(Control!$B$7&lt;H127,0,IF(Control!$B$7&gt;=I127,1,(Control!$B$7-H127+1)/J127))</f>
@@ -14260,7 +14270,7 @@
     </row>
     <row r="128" spans="1:23">
       <c r="A128" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B128" t="s">
         <v>39</v>
@@ -14269,16 +14279,16 @@
         <v>40</v>
       </c>
       <c r="D128" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E128" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F128" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G128" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H128">
         <v>82</v>
@@ -14296,10 +14306,10 @@
         <v>57</v>
       </c>
       <c r="M128" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N128" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="P128" s="14">
         <f>IF(Control!$B$7&lt;H128,0,IF(Control!$B$7&gt;=I128,1,(Control!$B$7-H128+1)/J128))</f>
@@ -14333,7 +14343,7 @@
     </row>
     <row r="129" spans="1:23">
       <c r="A129" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B129" t="s">
         <v>39</v>
@@ -14342,16 +14352,16 @@
         <v>40</v>
       </c>
       <c r="D129" t="s">
+        <v>701</v>
+      </c>
+      <c r="E129" t="s">
+        <v>702</v>
+      </c>
+      <c r="F129" t="s">
         <v>703</v>
       </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>704</v>
-      </c>
-      <c r="F129" t="s">
-        <v>705</v>
-      </c>
-      <c r="G129" t="s">
-        <v>706</v>
       </c>
       <c r="H129">
         <v>79</v>
@@ -14369,10 +14379,10 @@
         <v>57</v>
       </c>
       <c r="M129" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="N129" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="P129" s="14">
         <f>IF(Control!$B$7&lt;H129,0,IF(Control!$B$7&gt;=I129,1,(Control!$B$7-H129+1)/J129))</f>
@@ -14406,7 +14416,7 @@
     </row>
     <row r="130" spans="1:23">
       <c r="A130" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B130" t="s">
         <v>39</v>
@@ -14415,16 +14425,16 @@
         <v>40</v>
       </c>
       <c r="D130" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E130" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F130" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G130" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H130">
         <v>80</v>
@@ -14442,10 +14452,10 @@
         <v>57</v>
       </c>
       <c r="M130" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="N130" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="P130" s="14">
         <f>IF(Control!$B$7&lt;H130,0,IF(Control!$B$7&gt;=I130,1,(Control!$B$7-H130+1)/J130))</f>
@@ -14479,7 +14489,7 @@
     </row>
     <row r="131" spans="1:23">
       <c r="A131" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B131" t="s">
         <v>39</v>
@@ -14488,16 +14498,16 @@
         <v>40</v>
       </c>
       <c r="D131" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E131" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F131" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="G131" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H131">
         <v>82</v>
@@ -14515,10 +14525,10 @@
         <v>57</v>
       </c>
       <c r="M131" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="N131" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="P131" s="14">
         <f>IF(Control!$B$7&lt;H131,0,IF(Control!$B$7&gt;=I131,1,(Control!$B$7-H131+1)/J131))</f>
@@ -14552,7 +14562,7 @@
     </row>
     <row r="132" spans="1:23">
       <c r="A132" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B132" t="s">
         <v>39</v>
@@ -14561,16 +14571,16 @@
         <v>40</v>
       </c>
       <c r="D132" t="s">
+        <v>716</v>
+      </c>
+      <c r="E132" t="s">
+        <v>717</v>
+      </c>
+      <c r="F132" t="s">
         <v>718</v>
       </c>
-      <c r="E132" t="s">
-        <v>719</v>
-      </c>
-      <c r="F132" t="s">
-        <v>720</v>
-      </c>
       <c r="G132" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H132">
         <v>85</v>
@@ -14588,10 +14598,10 @@
         <v>57</v>
       </c>
       <c r="M132" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="N132" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="P132" s="14">
         <f>IF(Control!$B$7&lt;H132,0,IF(Control!$B$7&gt;=I132,1,(Control!$B$7-H132+1)/J132))</f>
@@ -14625,7 +14635,7 @@
     </row>
     <row r="133" spans="1:23">
       <c r="A133" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B133" t="s">
         <v>39</v>
@@ -14634,16 +14644,16 @@
         <v>40</v>
       </c>
       <c r="D133" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E133" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F133" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G133" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H133">
         <v>86</v>
@@ -14661,10 +14671,10 @@
         <v>57</v>
       </c>
       <c r="M133" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="N133" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="P133" s="14">
         <f>IF(Control!$B$7&lt;H133,0,IF(Control!$B$7&gt;=I133,1,(Control!$B$7-H133+1)/J133))</f>
@@ -14698,7 +14708,7 @@
     </row>
     <row r="134" spans="1:23">
       <c r="A134" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B134" t="s">
         <v>39</v>
@@ -14707,16 +14717,16 @@
         <v>40</v>
       </c>
       <c r="D134" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E134" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F134" t="s">
-        <v>730</v>
+        <v>1046</v>
       </c>
       <c r="G134" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="H134">
         <v>87</v>
@@ -14734,10 +14744,10 @@
         <v>57</v>
       </c>
       <c r="M134" t="s">
-        <v>731</v>
+        <v>1047</v>
       </c>
       <c r="N134" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="P134" s="14">
         <f>IF(Control!$B$7&lt;H134,0,IF(Control!$B$7&gt;=I134,1,(Control!$B$7-H134+1)/J134))</f>
@@ -14771,7 +14781,7 @@
     </row>
     <row r="135" spans="1:23">
       <c r="A135" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B135" t="s">
         <v>39</v>
@@ -14780,16 +14790,16 @@
         <v>40</v>
       </c>
       <c r="D135" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E135" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F135" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G135" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="H135">
         <v>88</v>
@@ -14807,10 +14817,10 @@
         <v>57</v>
       </c>
       <c r="M135" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="N135" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="P135" s="14">
         <f>IF(Control!$B$7&lt;H135,0,IF(Control!$B$7&gt;=I135,1,(Control!$B$7-H135+1)/J135))</f>
@@ -14844,7 +14854,7 @@
     </row>
     <row r="136" spans="1:23">
       <c r="A136" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B136" t="s">
         <v>39</v>
@@ -14853,16 +14863,16 @@
         <v>40</v>
       </c>
       <c r="D136" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E136" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F136" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="G136" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="H136">
         <v>89</v>
@@ -14880,10 +14890,10 @@
         <v>57</v>
       </c>
       <c r="M136" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="N136" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="P136" s="14">
         <f>IF(Control!$B$7&lt;H136,0,IF(Control!$B$7&gt;=I136,1,(Control!$B$7-H136+1)/J136))</f>
@@ -14917,7 +14927,7 @@
     </row>
     <row r="137" spans="1:23">
       <c r="A137" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B137" t="s">
         <v>39</v>
@@ -14926,16 +14936,16 @@
         <v>40</v>
       </c>
       <c r="D137" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E137" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F137" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="G137" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="H137">
         <v>90</v>
@@ -14953,10 +14963,10 @@
         <v>57</v>
       </c>
       <c r="M137" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="N137" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="O137" t="s">
         <v>41</v>
@@ -15077,7 +15087,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5">
       <c r="A1" s="26" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -15120,13 +15130,13 @@
         <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -15455,22 +15465,22 @@
       </c>
       <c r="H11" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A11,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A11,WBS!$R$5:$R$137),0)</f>
-        <v>0.75000000000000011</v>
+        <v>1</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="0"/>
-        <v>0.75000000000000011</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4">
         <v>3</v>
       </c>
       <c r="K11" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A11,WBS!$U$5:$U$137,"Complete")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="4" t="str">
         <f>IF(H11&gt;=1,"Complete",IF(H11&gt;0,"In Progress",IF(Control!$B$7&lt;D11,"Not Started",IF(Control!$B$7&gt;E11,"Late","Ready"))))</f>
-        <v>In Progress</v>
+        <v>Complete</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -15481,7 +15491,7 @@
         <v>27</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>228</v>
+        <v>1044</v>
       </c>
       <c r="D12" s="4">
         <v>15</v>
@@ -15518,13 +15528,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D13" s="4">
         <v>18</v>
@@ -15561,13 +15571,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D14" s="4">
         <v>15</v>
@@ -15604,13 +15614,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D15" s="4">
         <v>22</v>
@@ -15647,13 +15657,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D16" s="4">
         <v>22</v>
@@ -15690,13 +15700,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D17" s="4">
         <v>26</v>
@@ -15733,13 +15743,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D18" s="4">
         <v>29</v>
@@ -15776,13 +15786,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D19" s="4">
         <v>35</v>
@@ -15819,13 +15829,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D20" s="4">
         <v>38</v>
@@ -15862,13 +15872,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D21" s="4">
         <v>41</v>
@@ -15905,13 +15915,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D22" s="4">
         <v>45</v>
@@ -15948,13 +15958,13 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D23" s="4">
         <v>38</v>
@@ -15991,13 +16001,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D24" s="4">
         <v>48</v>
@@ -16034,13 +16044,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D25" s="4">
         <v>51</v>
@@ -16077,13 +16087,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D26" s="4">
         <v>35</v>
@@ -16120,13 +16130,13 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D27" s="4">
         <v>57</v>
@@ -16163,13 +16173,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D28" s="4">
         <v>57</v>
@@ -16206,13 +16216,13 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D29" s="4">
         <v>61</v>
@@ -16249,13 +16259,13 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D30" s="4">
         <v>63</v>
@@ -16292,13 +16302,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D31" s="4">
         <v>65</v>
@@ -16335,13 +16345,13 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D32" s="4">
         <v>68</v>
@@ -16378,13 +16388,13 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D33" s="4">
         <v>69</v>
@@ -16421,13 +16431,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D34" s="4">
         <v>71</v>
@@ -16464,13 +16474,13 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D35" s="4">
         <v>73</v>
@@ -16507,13 +16517,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D36" s="4">
         <v>75</v>
@@ -16550,13 +16560,13 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D37" s="4">
         <v>76</v>
@@ -16593,13 +16603,13 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D38" s="4">
         <v>79</v>
@@ -16636,13 +16646,13 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D39" s="4">
         <v>79</v>
@@ -16679,13 +16689,13 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D40" s="4">
         <v>79</v>
@@ -16722,13 +16732,13 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="4" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D41" s="4">
         <v>85</v>
@@ -16765,13 +16775,13 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D42" s="4">
         <v>87</v>
@@ -16808,13 +16818,13 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="D43" s="4">
         <v>89</v>
@@ -16917,7 +16927,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5">
       <c r="A1" s="27" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -16930,31 +16940,31 @@
     </row>
     <row r="3" spans="1:9" ht="30">
       <c r="A3" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="42.75">
@@ -16968,20 +16978,20 @@
         <v>46222</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="H4" s="6">
         <v>1.0899182561307902E-2</v>
       </c>
       <c r="I4" s="6">
         <f>IF(A4=Control!$B$7,Control!$B$11,"")</f>
-        <v>0.18746594005449582</v>
+        <v>0.19291553133514977</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="42.75">
@@ -16995,13 +17005,13 @@
         <v>46229</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="H5" s="6">
         <v>2.7247956403269755E-2</v>
@@ -17022,13 +17032,13 @@
         <v>46236</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="H6" s="6">
         <v>4.3596730245231599E-2</v>
@@ -17049,13 +17059,13 @@
         <v>46243</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="H7" s="6">
         <v>5.9945504087193451E-2</v>
@@ -17076,13 +17086,13 @@
         <v>46250</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="H8" s="6">
         <v>7.0844686648501354E-2</v>
@@ -17103,16 +17113,16 @@
         <v>46257</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="H9" s="6">
         <v>8.2833787465940042E-2</v>
@@ -17133,13 +17143,13 @@
         <v>46264</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="H10" s="6">
         <v>9.3732970027247939E-2</v>
@@ -17160,13 +17170,13 @@
         <v>46271</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H11" s="6">
         <v>0.11008174386920978</v>
@@ -17187,13 +17197,13 @@
         <v>46278</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="H12" s="6">
         <v>0.12643051771117164</v>
@@ -17214,13 +17224,13 @@
         <v>46285</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="H13" s="6">
         <v>0.13732970027247954</v>
@@ -17241,13 +17251,13 @@
         <v>46292</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="H14" s="6">
         <v>0.15367847411444138</v>
@@ -17268,16 +17278,16 @@
         <v>46299</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H15" s="6">
         <v>0.17111716621253403</v>
@@ -17298,13 +17308,13 @@
         <v>46306</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="H16" s="6">
         <v>0.18201634877384193</v>
@@ -17325,13 +17335,13 @@
         <v>46313</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="H17" s="6">
         <v>0.19291553133514983</v>
@@ -17352,13 +17362,13 @@
         <v>46320</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="H18" s="6">
         <v>0.20926430517711167</v>
@@ -17379,13 +17389,13 @@
         <v>46327</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="H19" s="6">
         <v>0.22561307901907351</v>
@@ -17406,13 +17416,13 @@
         <v>46334</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="H20" s="6">
         <v>0.23651226158038141</v>
@@ -17433,13 +17443,13 @@
         <v>46341</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="H21" s="6">
         <v>0.25286103542234328</v>
@@ -17460,13 +17470,13 @@
         <v>46348</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="H22" s="6">
         <v>0.26376021798365124</v>
@@ -17487,13 +17497,13 @@
         <v>46355</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="H23" s="6">
         <v>0.27465940054495913</v>
@@ -17514,13 +17524,13 @@
         <v>46362</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="H24" s="6">
         <v>0.28555858310626708</v>
@@ -17541,13 +17551,13 @@
         <v>46369</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H25" s="6">
         <v>0.30190735694822901</v>
@@ -17568,13 +17578,13 @@
         <v>46376</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="H26" s="6">
         <v>0.31825613079019088</v>
@@ -17595,13 +17605,13 @@
         <v>46383</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="H27" s="6">
         <v>0.34005449591280668</v>
@@ -17622,13 +17632,13 @@
         <v>46390</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="H28" s="6">
         <v>0.35095367847411457</v>
@@ -17649,13 +17659,13 @@
         <v>46397</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H29" s="6">
         <v>0.36185286103542252</v>
@@ -17676,13 +17686,13 @@
         <v>46404</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="H30" s="6">
         <v>0.37275204359673042</v>
@@ -17703,13 +17713,13 @@
         <v>46411</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="H31" s="6">
         <v>0.38365122615803832</v>
@@ -17730,13 +17740,13 @@
         <v>46418</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="H32" s="6">
         <v>0.39455040871934627</v>
@@ -17757,13 +17767,13 @@
         <v>46425</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="H33" s="6">
         <v>0.40544959128065416</v>
@@ -17784,13 +17794,13 @@
         <v>46432</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="H34" s="6">
         <v>0.41634877384196206</v>
@@ -17811,10 +17821,10 @@
         <v>46439</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="H35" s="6">
         <v>0.42343324250681219</v>
@@ -17835,16 +17845,16 @@
         <v>46446</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="H36" s="6">
         <v>0.43760217983651245</v>
@@ -17865,16 +17875,16 @@
         <v>46453</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="H37" s="6">
         <v>0.44468664850136258</v>
@@ -17895,13 +17905,13 @@
         <v>46460</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="H38" s="6">
         <v>0.45558583106267053</v>
@@ -17922,13 +17932,13 @@
         <v>46467</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="H39" s="6">
         <v>0.46648501362397843</v>
@@ -17949,13 +17959,13 @@
         <v>46474</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="H40" s="6">
         <v>0.4719346049046324</v>
@@ -17976,13 +17986,13 @@
         <v>46481</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H41" s="6">
         <v>0.48283378746594036</v>
@@ -18003,13 +18013,13 @@
         <v>46488</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="H42" s="6">
         <v>0.49918256130790223</v>
@@ -18030,13 +18040,13 @@
         <v>46495</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="H43" s="6">
         <v>0.51553133514986416</v>
@@ -18057,13 +18067,13 @@
         <v>46502</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="H44" s="6">
         <v>0.52643051771117211</v>
@@ -18084,13 +18094,13 @@
         <v>46509</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="H45" s="6">
         <v>0.54277929155313398</v>
@@ -18111,13 +18121,13 @@
         <v>46516</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="H46" s="6">
         <v>0.55912806539509574</v>
@@ -18138,13 +18148,13 @@
         <v>46523</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="H47" s="6">
         <v>0.57547683923705772</v>
@@ -18165,13 +18175,13 @@
         <v>46530</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="H48" s="6">
         <v>0.58092643051771164</v>
@@ -18192,13 +18202,13 @@
         <v>46537</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="H49" s="6">
         <v>0.59182561307901949</v>
@@ -18219,13 +18229,13 @@
         <v>46544</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="H50" s="6">
         <v>0.60272479564032744</v>
@@ -18246,13 +18256,13 @@
         <v>46551</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="H51" s="6">
         <v>0.60817438692098136</v>
@@ -18273,13 +18283,13 @@
         <v>46558</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="H52" s="6">
         <v>0.61362397820163528</v>
@@ -18300,13 +18310,13 @@
         <v>46565</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="H53" s="6">
         <v>0.62452316076294312</v>
@@ -18327,13 +18337,13 @@
         <v>46572</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="H54" s="6">
         <v>0.63542234332425096</v>
@@ -18354,13 +18364,13 @@
         <v>46579</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H55" s="6">
         <v>0.64087193460490499</v>
@@ -18381,13 +18391,13 @@
         <v>46586</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="H56" s="6">
         <v>0.65177111716621283</v>
@@ -18408,13 +18418,13 @@
         <v>46593</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="H57" s="6">
         <v>0.6681198910081747</v>
@@ -18435,16 +18445,16 @@
         <v>46600</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="H58" s="6">
         <v>0.67574931880109024</v>
@@ -18465,16 +18475,16 @@
         <v>46607</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="H59" s="6">
         <v>0.68337874659400577</v>
@@ -18495,13 +18505,13 @@
         <v>46614</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="H60" s="6">
         <v>0.69427792915531361</v>
@@ -18522,13 +18532,13 @@
         <v>46621</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="H61" s="6">
         <v>0.71062670299727548</v>
@@ -18549,13 +18559,13 @@
         <v>46628</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="H62" s="6">
         <v>0.7160762942779294</v>
@@ -18576,13 +18586,13 @@
         <v>46635</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="H63" s="6">
         <v>0.72152588555858332</v>
@@ -18603,13 +18613,13 @@
         <v>46642</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="H64" s="6">
         <v>0.72697547683923724</v>
@@ -18630,13 +18640,13 @@
         <v>46649</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="H65" s="6">
         <v>0.73787465940054509</v>
@@ -18657,13 +18667,13 @@
         <v>46656</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="H66" s="6">
         <v>0.74332425068119901</v>
@@ -18684,13 +18694,13 @@
         <v>46663</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="H67" s="6">
         <v>0.74877384196185293</v>
@@ -18711,13 +18721,13 @@
         <v>46670</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="H68" s="6">
         <v>0.75967302452316077</v>
@@ -18738,13 +18748,13 @@
         <v>46677</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="H69" s="6">
         <v>0.76512261580381469</v>
@@ -18765,13 +18775,13 @@
         <v>46684</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H70" s="6">
         <v>0.77057220708446861</v>
@@ -18792,13 +18802,13 @@
         <v>46691</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="H71" s="6">
         <v>0.78147138964577645</v>
@@ -18819,13 +18829,13 @@
         <v>46698</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="H72" s="6">
         <v>0.79237057220708429</v>
@@ -18846,16 +18856,16 @@
         <v>46705</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="H73" s="6">
         <v>0.80054495912806523</v>
@@ -18876,13 +18886,13 @@
         <v>46712</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="H74" s="6">
         <v>0.80599455040871915</v>
@@ -18903,13 +18913,13 @@
         <v>46719</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="H75" s="6">
         <v>0.81144414168937307</v>
@@ -18930,13 +18940,13 @@
         <v>46726</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="H76" s="6">
         <v>0.82234332425068091</v>
@@ -18957,13 +18967,13 @@
         <v>46733</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="H77" s="6">
         <v>0.83324250681198875</v>
@@ -18984,13 +18994,13 @@
         <v>46740</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="H78" s="6">
         <v>0.84414168937329659</v>
@@ -19011,13 +19021,13 @@
         <v>46747</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="H79" s="6">
         <v>0.84959128065395051</v>
@@ -19038,13 +19048,13 @@
         <v>46754</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="H80" s="6">
         <v>0.85504087193460443</v>
@@ -19065,16 +19075,16 @@
         <v>46761</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="H81" s="6">
         <v>0.8713896457765663</v>
@@ -19095,13 +19105,13 @@
         <v>46768</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="H82" s="6">
         <v>0.88773841961852806</v>
@@ -19122,13 +19132,13 @@
         <v>46775</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="H83" s="6">
         <v>0.90408719346048982</v>
@@ -19149,13 +19159,13 @@
         <v>46782</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="H84" s="6">
         <v>0.91498637602179789</v>
@@ -19176,10 +19186,10 @@
         <v>46789</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="H85" s="6">
         <v>0.92425068119890952</v>
@@ -19200,10 +19210,10 @@
         <v>46796</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="H86" s="6">
         <v>0.93351498637602137</v>
@@ -19224,13 +19234,13 @@
         <v>46803</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="H87" s="6">
         <v>0.942779291553133</v>
@@ -19251,13 +19261,13 @@
         <v>46810</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="H88" s="6">
         <v>0.95204359673024475</v>
@@ -19278,13 +19288,13 @@
         <v>46817</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="H89" s="6">
         <v>0.96130790190735638</v>
@@ -19305,13 +19315,13 @@
         <v>46824</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>1000</v>
+        <v>1048</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>1001</v>
+        <v>1049</v>
       </c>
       <c r="H90" s="6">
         <v>0.97057220708446812</v>
@@ -19332,13 +19342,13 @@
         <v>46831</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="H91" s="6">
         <v>0.97983651226157975</v>
@@ -19359,13 +19369,13 @@
         <v>46838</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="H92" s="6">
         <v>0.98910081743869149</v>
@@ -19386,16 +19396,16 @@
         <v>46845</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="H93" s="6">
         <v>0.99999999999999933</v>
@@ -19471,7 +19481,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5">
       <c r="A1" s="26" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -19483,71 +19493,71 @@
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="8" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="4" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28.5">
       <c r="A7" s="4" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" s="22" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -19562,13 +19572,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.5">
@@ -19579,7 +19589,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>150</v>
@@ -19593,7 +19603,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>207</v>
@@ -19607,10 +19617,10 @@
         <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.5">
@@ -19621,10 +19631,10 @@
         <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -19635,10 +19645,10 @@
         <v>70</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.5">
@@ -19649,10 +19659,10 @@
         <v>78</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.5">
@@ -19663,15 +19673,15 @@
         <v>90</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15">
       <c r="A22" s="22" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -19686,7 +19696,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -19694,7 +19704,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -19702,7 +19712,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -19710,7 +19720,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -19718,7 +19728,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -19726,7 +19736,7 @@
         <v>6</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>

--- a/ESP32_S3_SQD_Project_WBS.xlsx
+++ b/ESP32_S3_SQD_Project_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f91d42a59b2d5e5/SQD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7B4A80D-B986-4F5E-91F4-2A851EA0D048}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{97F445B2-9959-4A2B-953A-FF2A2BEAA89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47CDC085-51F7-4468-A5D0-052B2B32A254}"/>
   <bookViews>
     <workbookView xWindow="-14730" yWindow="-16320" windowWidth="57840" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1053">
   <si>
     <t>ESP32-S3 Solo Program Dashboard</t>
   </si>
@@ -3328,6 +3328,12 @@
   </si>
   <si>
     <t>Gate G-C accepted 2026-08-02 | Record: docs/phase-c/C1.3_Architecture_Review_and_Gate.md | PR: https://github.com/CPParthasarathy/SQD/pull/23 | Accepted main: bd995912fb5632394f6aa29b146f17ec9dcdcf6d | CI: https://github.com/CPParthasarathy/SQD/actions/runs/30745138225 (4/4 PASS) | Architecture: 11/11 PASS | C1.3 tests: 6/6 PASS | Host tests: 38/38 PASS</t>
+  </si>
+  <si>
+    <t>Document: docs/phase-c/C2.1_Board_Pins_Revision_Detection.md | Accepted main: d16f0d3223fa8d895f65837450acb346d3256b22 | Result: board-pin, active-level, pull, electrical-capability and revision-detection contract accepted, synchronized and closed</t>
+  </si>
+  <si>
+    <t>Document: docs/phase-c/C2.2_Board_Support_Implementation.md | Accepted main: 974b56aacb975b8dd719432389f34b01772eba68 | Result: static board contract PASS; 57 host tests PASS; ESP-IDF 6.0.2 isolated build PASS; GitHub Actions green; squash merge accepted, synchronized and closed</t>
   </si>
 </sst>
 </file>
@@ -3843,7 +3849,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.9681274900398433E-2</c:v>
+                  <c:v>0.13944223107569725</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4331,14 +4337,14 @@
       </c>
       <c r="E5" s="12">
         <f>Control!B11</f>
-        <v>0.19291553133514977</v>
+        <v>0.20926430517711161</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H5" s="12">
         <f>Control!B12</f>
-        <v>0.18201634877384187</v>
+        <v>0.19836512261580372</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1"/>
@@ -4355,7 +4361,7 @@
       </c>
       <c r="E7" s="11">
         <f>Control!B14</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>9</v>
@@ -4501,11 +4507,11 @@
       </c>
       <c r="F14" s="6">
         <f>IFERROR(SUMIF(WBS!$B$5:$B$137,A14,WBS!$T$5:$T$137)/SUMIF(WBS!$B$5:$B$137,A14,WBS!$R$5:$R$137),0)</f>
-        <v>7.9681274900398433E-2</v>
+        <v>0.13944223107569725</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" si="0"/>
-        <v>7.9681274900398433E-2</v>
+        <v>0.13944223107569725</v>
       </c>
       <c r="H14" s="4">
         <f>COUNTIF(WBS!$B$5:$B$137,A14)</f>
@@ -4513,7 +4519,7 @@
       </c>
       <c r="I14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Complete")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4">
         <f>COUNTIFS(WBS!$B$5:$B$137,A14,WBS!$U$5:$U$137,"Late")</f>
@@ -4960,7 +4966,7 @@
       </c>
       <c r="B11" s="6">
         <f>SUM(WBS!T5:T137)</f>
-        <v>0.19291553133514977</v>
+        <v>0.20926430517711161</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>69</v>
@@ -4975,7 +4981,7 @@
       </c>
       <c r="B12" s="6">
         <f>B11-B10</f>
-        <v>0.18201634877384187</v>
+        <v>0.19836512261580372</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>70</v>
@@ -5005,7 +5011,7 @@
       </c>
       <c r="B14" s="4">
         <f>COUNTIF(WBS!U5:U137,"Complete")</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>72</v>
@@ -7141,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="14">
         <f t="shared" si="0"/>
@@ -7153,17 +7159,20 @@
       </c>
       <c r="T30" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.4495912806539499E-3</v>
       </c>
       <c r="U30" t="str">
         <f>IF(Q30&gt;=1,"Complete",IF(Q30&gt;0,"In Progress",IF(Control!$B$7&lt;H30,"Not Started",IF(Control!$B$7&gt;I30,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V30" s="15">
         <v>46314</v>
       </c>
       <c r="W30" s="15">
         <v>46320</v>
+      </c>
+      <c r="X30" t="s">
+        <v>1051</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -7214,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="14">
         <f t="shared" si="0"/>
@@ -7226,17 +7235,20 @@
       </c>
       <c r="T31" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.08991825613079E-2</v>
       </c>
       <c r="U31" t="str">
         <f>IF(Q31&gt;=1,"Complete",IF(Q31&gt;0,"In Progress",IF(Control!$B$7&lt;H31,"Not Started",IF(Control!$B$7&gt;I31,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>Complete</v>
       </c>
       <c r="V31" s="15">
         <v>46314</v>
       </c>
       <c r="W31" s="15">
         <v>46327</v>
+      </c>
+      <c r="X31" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -15508,22 +15520,22 @@
       </c>
       <c r="H12" s="6">
         <f>IFERROR(SUMIF(WBS!$D$5:$D$137,A12,WBS!$T$5:$T$137)/SUMIF(WBS!$D$5:$D$137,A12,WBS!$R$5:$R$137),0)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J12" s="4">
         <v>3</v>
       </c>
       <c r="K12" s="4">
         <f>COUNTIFS(WBS!$D$5:$D$137,A12,WBS!$U$5:$U$137,"Complete")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="4" t="str">
         <f>IF(H12&gt;=1,"Complete",IF(H12&gt;0,"In Progress",IF(Control!$B$7&lt;D12,"Not Started",IF(Control!$B$7&gt;E12,"Late","Ready"))))</f>
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -16991,7 +17003,7 @@
       </c>
       <c r="I4" s="6">
         <f>IF(A4=Control!$B$7,Control!$B$11,"")</f>
-        <v>0.19291553133514977</v>
+        <v>0.20926430517711161</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="42.75">
